--- a/templates/approved/8. АОСР ВЛ1.xlsx
+++ b/templates/approved/8. АОСР ВЛ1.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="183">
   <si>
     <t>(исполнительные схемы и чертежи, результаты экспертиз, обследований, лабораторных и иных испытаний)</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>приложение №3</t>
+  </si>
+  <si>
+    <t>Приказ Минстроя  №344/пр от 16.05.2023</t>
   </si>
   <si>
     <t>Застройщик, технический заказчик, лицо, ответственное за  эксплуатацию здания, сооружения, или региональный оператор</t>
@@ -439,9 +442,6 @@
   </si>
   <si>
     <t>1.</t>
-  </si>
-  <si>
-    <t>1шурф</t>
   </si>
   <si>
     <t>Стойка железобетонная</t>
@@ -2001,7 +2001,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AJ1" s="21"/>
+      <c r="AJ1" s="21" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" spans="1:43" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AJ2" s="21" t="s">
@@ -2023,7 +2025,7 @@
     </row>
     <row r="4" spans="1:43" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="138" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
@@ -2063,7 +2065,7 @@
     </row>
     <row r="5" spans="1:43" s="20" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138" t="str">
-        <f>'Данные объект'!B9</f>
+        <f>IF('Данные объект'!B9="","",'Данные объект'!B9)</f>
       </c>
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
@@ -2143,7 +2145,7 @@
     </row>
     <row r="7" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="137"/>
       <c r="C7" s="137"/>
@@ -2183,7 +2185,7 @@
     </row>
     <row r="8" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="146" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="B8" s="146"/>
       <c r="C8" s="146"/>
@@ -2223,7 +2225,7 @@
     </row>
     <row r="9" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="140"/>
       <c r="C9" s="140"/>
@@ -2263,7 +2265,7 @@
     </row>
     <row r="10" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="146" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="B10" s="146"/>
       <c r="C10" s="146"/>
@@ -2303,7 +2305,7 @@
     </row>
     <row r="11" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="140"/>
       <c r="C11" s="140"/>
@@ -2343,7 +2345,7 @@
     </row>
     <row r="12" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="146" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="B12" s="146"/>
       <c r="C12" s="146"/>
@@ -2383,7 +2385,7 @@
     </row>
     <row r="13" spans="1:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="140"/>
       <c r="C13" s="140"/>
@@ -2428,7 +2430,7 @@
     </row>
     <row r="15" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="146" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B15" s="146"/>
       <c r="C15" s="146"/>
@@ -2508,7 +2510,7 @@
     </row>
     <row r="17" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B17" s="146"/>
       <c r="C17" s="146"/>
@@ -2548,7 +2550,7 @@
     </row>
     <row r="18" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="140"/>
       <c r="C18" s="140"/>
@@ -2588,7 +2590,7 @@
     </row>
     <row r="19" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B19" s="146"/>
       <c r="C19" s="146"/>
@@ -2628,7 +2630,7 @@
     </row>
     <row r="20" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="140"/>
       <c r="C20" s="140"/>
@@ -2673,7 +2675,7 @@
     </row>
     <row r="22" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="146" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="B22" s="146"/>
       <c r="C22" s="146"/>
@@ -2753,7 +2755,7 @@
     </row>
     <row r="24" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B24" s="146"/>
       <c r="C24" s="146"/>
@@ -2793,7 +2795,7 @@
     </row>
     <row r="25" spans="1:36" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="140"/>
       <c r="C25" s="140"/>
@@ -2833,7 +2835,7 @@
     </row>
     <row r="26" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B26" s="146"/>
       <c r="C26" s="146"/>
@@ -2873,7 +2875,7 @@
     </row>
     <row r="27" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" s="140"/>
       <c r="C27" s="140"/>
@@ -3026,11 +3028,11 @@
         <v>18</v>
       </c>
       <c r="C32" s="134">
-        <f>'АОСР-6'!C32:D32+1</f>
+        <f>IF('АОСР-6'!C32="","",'АОСР-6'!C32+1)</f>
       </c>
       <c r="D32" s="134"/>
       <c r="E32" s="134" t="str">
-        <f>'АОСР-1'!E33</f>
+        <f>IF('АОСР-1'!E33="","",'АОСР-1'!E33)</f>
       </c>
       <c r="F32" s="134"/>
       <c r="G32" s="134"/>
@@ -3041,7 +3043,7 @@
       <c r="Y32" s="35"/>
       <c r="Z32" s="35"/>
       <c r="AB32" s="142">
-        <f>P78</f>
+        <f>IF(P78="","",P78)</f>
       </c>
       <c r="AC32" s="142"/>
       <c r="AD32" s="142"/>
@@ -3078,7 +3080,7 @@
     </row>
     <row r="35" spans="1:36" s="20" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="137"/>
       <c r="C35" s="137"/>
@@ -3118,7 +3120,7 @@
     </row>
     <row r="36" spans="1:36" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="138" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="B36" s="138"/>
       <c r="C36" s="138"/>
@@ -3158,7 +3160,7 @@
     </row>
     <row r="37" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B37" s="140"/>
       <c r="C37" s="140"/>
@@ -3198,7 +3200,7 @@
     </row>
     <row r="38" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="138" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -3238,7 +3240,7 @@
     </row>
     <row r="39" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="151"/>
@@ -3283,7 +3285,7 @@
     </row>
     <row r="41" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="146" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
       <c r="B41" s="146"/>
       <c r="C41" s="146"/>
@@ -3363,7 +3365,7 @@
     </row>
     <row r="43" spans="1:36" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -3403,7 +3405,7 @@
     </row>
     <row r="44" spans="1:36" s="28" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="138" t="str">
-        <f>'Данные объект'!C18</f>
+        <f>IF('Данные объект'!C18="","",'Данные объект'!C18)</f>
       </c>
       <c r="B44" s="138"/>
       <c r="C44" s="138"/>
@@ -3443,7 +3445,7 @@
     </row>
     <row r="45" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="140"/>
       <c r="C45" s="140"/>
@@ -3523,7 +3525,7 @@
     </row>
     <row r="47" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="138" t="str">
-        <f>'Данные объект'!$C$36</f>
+        <f>IF('Данные объект'!$C$36="","",'Данные объект'!$C$36)</f>
       </c>
       <c r="B47" s="138"/>
       <c r="C47" s="138"/>
@@ -3603,7 +3605,7 @@
     </row>
     <row r="49" spans="1:36" s="20" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" s="143"/>
       <c r="C49" s="143"/>
@@ -3681,7 +3683,7 @@
     </row>
     <row r="51" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" s="140"/>
       <c r="C51" s="140"/>
@@ -3721,7 +3723,7 @@
     </row>
     <row r="52" spans="1:36" s="20" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="143"/>
@@ -3877,7 +3879,7 @@
     </row>
     <row r="56" spans="1:36" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="139"/>
       <c r="C56" s="139"/>
@@ -3922,7 +3924,7 @@
     </row>
     <row r="58" spans="1:36" s="20" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="134" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B58" s="134"/>
       <c r="C58" s="134"/>
@@ -4011,8 +4013,8 @@
       </c>
     </row>
     <row r="62" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="60" t="str">
-        <f>'АОСР-6'!A86:AJ86</f>
+      <c r="A62" s="60">
+        <f>IF('АОСР-6'!A86="","",'АОСР-6'!A86)</f>
       </c>
       <c r="B62" s="60"/>
       <c r="C62" s="60"/>
@@ -4022,7 +4024,7 @@
       <c r="G62" s="60"/>
       <c r="H62" s="60"/>
       <c r="I62" s="146" t="str">
-        <f>'АОСР-1'!O63</f>
+        <f>IF('АОСР-1'!O63="","",'АОСР-1'!O63)</f>
       </c>
       <c r="J62" s="146"/>
       <c r="K62" s="146"/>
@@ -4103,7 +4105,7 @@
     </row>
     <row r="65" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="138" t="str">
-        <f>'Данные объект'!B43</f>
+        <f>IF('Данные объект'!B43="","",'Данные объект'!B43)</f>
       </c>
       <c r="B65" s="138"/>
       <c r="C65" s="138"/>
@@ -4224,7 +4226,7 @@
       <c r="N68" s="9"/>
       <c r="O68" s="9"/>
       <c r="P68" s="136" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q68" s="136"/>
       <c r="R68" s="136"/>
@@ -4257,11 +4259,9 @@
       <c r="E69" s="165"/>
       <c r="F69" s="165"/>
       <c r="G69" s="115" t="s">
-        <v>72</v>
-      </c>
-      <c r="H69" s="166">
-        <v>12</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H69" s="166"/>
       <c r="I69" s="166"/>
       <c r="J69" s="116" t="s">
         <v>182</v>
@@ -4305,7 +4305,7 @@
       <c r="E70" s="161"/>
       <c r="F70" s="161"/>
       <c r="G70" s="104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H70" s="157"/>
       <c r="I70" s="157"/>
@@ -4551,7 +4551,7 @@
       <c r="M77" s="35"/>
       <c r="N77" s="35"/>
       <c r="P77" s="142">
-        <f>'Данные объект'!B6</f>
+        <f>IF('Данные объект'!B6="","",'Данные объект'!B6)</f>
       </c>
       <c r="Q77" s="142"/>
       <c r="R77" s="142"/>
@@ -4576,7 +4576,7 @@
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
       <c r="P78" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="Q78" s="142"/>
       <c r="R78" s="142"/>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="81" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B81" s="149"/>
       <c r="C81" s="149"/>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="84" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="135" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B84" s="135"/>
       <c r="C84" s="135"/>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="90" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H90" s="134"/>
       <c r="I90" s="134"/>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="93" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B93" s="162" t="str">
-        <f>R72</f>
+        <f>IF(R72="","",R72)</f>
       </c>
       <c r="C93" s="162"/>
       <c r="D93" s="162"/>
@@ -4923,10 +4923,10 @@
       <c r="O93" s="162"/>
       <c r="P93" s="162"/>
       <c r="Q93" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R93" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S93" s="18"/>
       <c r="T93" s="18"/>
@@ -4949,10 +4949,10 @@
     </row>
     <row r="94" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B94" s="162" t="str">
-        <f>L69</f>
+        <f>IF(L69="","",L69)</f>
       </c>
       <c r="C94" s="162"/>
       <c r="D94" s="162"/>
@@ -4969,10 +4969,10 @@
       <c r="O94" s="162"/>
       <c r="P94" s="162"/>
       <c r="Q94" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R94" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S94" s="18"/>
       <c r="T94" s="18"/>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="99" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="134" t="str">
-        <f>'Данные объект'!B33</f>
+        <f>IF('Данные объект'!B33="","",'Данные объект'!B33)</f>
       </c>
       <c r="B99" s="134"/>
       <c r="C99" s="134"/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="102" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="134" t="str">
-        <f>'Данные объект'!B20</f>
+        <f>IF('Данные объект'!B20="","",'Данные объект'!B20)</f>
       </c>
       <c r="B102" s="134"/>
       <c r="C102" s="134"/>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="106" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="134" t="str">
-        <f>'Данные объект'!B17</f>
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
       </c>
       <c r="B106" s="134"/>
       <c r="C106" s="134"/>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="109" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A109" s="134" t="str">
-        <f>'Данные объект'!$B$36</f>
+        <f>IF('Данные объект'!$B$36="","",'Данные объект'!$B$36)</f>
       </c>
       <c r="B109" s="134"/>
       <c r="C109" s="134"/>
@@ -5466,7 +5466,7 @@
     </row>
     <row r="111" spans="1:36" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B111" s="143"/>
       <c r="C111" s="143"/>
@@ -5506,7 +5506,7 @@
     </row>
     <row r="112" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B112" s="134"/>
       <c r="C112" s="134"/>
@@ -5535,7 +5535,7 @@
       <c r="Z112" s="35"/>
       <c r="AA112" s="35"/>
       <c r="AB112" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC112" s="134"/>
       <c r="AD112" s="134"/>
@@ -5590,7 +5590,7 @@
     </row>
     <row r="114" spans="1:36" s="20" customFormat="1" ht="11.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B114" s="143"/>
       <c r="C114" s="143"/>
@@ -5629,9 +5629,7 @@
       <c r="AJ114" s="143"/>
     </row>
     <row r="115" spans="1:36" s="20" customFormat="1" ht="11.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="134" t="e">
-        <f>#REF!</f>
-      </c>
+      <c r="A115" s="134"/>
       <c r="B115" s="134"/>
       <c r="C115" s="134"/>
       <c r="D115" s="134"/>
@@ -5844,7 +5842,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AJ1" s="21"/>
+      <c r="AJ1" s="21" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" spans="1:43" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AJ2" s="21" t="s">
@@ -5866,7 +5866,7 @@
     </row>
     <row r="4" spans="1:43" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="138" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="5" spans="1:43" s="20" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138" t="str">
-        <f>'Данные объект'!B9</f>
+        <f>IF('Данные объект'!B9="","",'Данные объект'!B9)</f>
       </c>
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
@@ -5986,7 +5986,7 @@
     </row>
     <row r="7" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="137"/>
       <c r="C7" s="137"/>
@@ -6026,7 +6026,7 @@
     </row>
     <row r="8" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="146" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="B8" s="146"/>
       <c r="C8" s="146"/>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="9" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="140"/>
       <c r="C9" s="140"/>
@@ -6106,7 +6106,7 @@
     </row>
     <row r="10" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="146" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="B10" s="146"/>
       <c r="C10" s="146"/>
@@ -6146,7 +6146,7 @@
     </row>
     <row r="11" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="140"/>
       <c r="C11" s="140"/>
@@ -6186,7 +6186,7 @@
     </row>
     <row r="12" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="146" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="B12" s="146"/>
       <c r="C12" s="146"/>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="13" spans="1:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="140"/>
       <c r="C13" s="140"/>
@@ -6271,7 +6271,7 @@
     </row>
     <row r="15" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="146" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B15" s="146"/>
       <c r="C15" s="146"/>
@@ -6351,7 +6351,7 @@
     </row>
     <row r="17" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B17" s="146"/>
       <c r="C17" s="146"/>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="18" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="140"/>
       <c r="C18" s="140"/>
@@ -6431,7 +6431,7 @@
     </row>
     <row r="19" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B19" s="146"/>
       <c r="C19" s="146"/>
@@ -6471,7 +6471,7 @@
     </row>
     <row r="20" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="140"/>
       <c r="C20" s="140"/>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="22" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="146" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="B22" s="146"/>
       <c r="C22" s="146"/>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="24" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B24" s="146"/>
       <c r="C24" s="146"/>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="25" spans="1:36" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="140"/>
       <c r="C25" s="140"/>
@@ -6676,7 +6676,7 @@
     </row>
     <row r="26" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B26" s="146"/>
       <c r="C26" s="146"/>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="27" spans="1:36" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" s="140"/>
       <c r="C27" s="140"/>
@@ -6868,12 +6868,10 @@
       <c r="B32" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="134" t="s">
-        <v>118</v>
-      </c>
+      <c r="C32" s="134"/>
       <c r="D32" s="134"/>
       <c r="E32" s="134" t="str">
-        <f>'АОСР-1'!E33</f>
+        <f>IF('АОСР-1'!E33="","",'АОСР-1'!E33)</f>
       </c>
       <c r="F32" s="134"/>
       <c r="G32" s="134"/>
@@ -6884,7 +6882,7 @@
       <c r="Y32" s="35"/>
       <c r="Z32" s="35"/>
       <c r="AB32" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="AC32" s="142"/>
       <c r="AD32" s="142"/>
@@ -6923,7 +6921,7 @@
     </row>
     <row r="35" spans="1:36" s="20" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="137"/>
       <c r="C35" s="137"/>
@@ -6963,7 +6961,7 @@
     </row>
     <row r="36" spans="1:36" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="138" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="B36" s="138"/>
       <c r="C36" s="138"/>
@@ -7003,7 +7001,7 @@
     </row>
     <row r="37" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B37" s="140"/>
       <c r="C37" s="140"/>
@@ -7043,7 +7041,7 @@
     </row>
     <row r="38" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="138" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -7083,7 +7081,7 @@
     </row>
     <row r="39" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="151"/>
@@ -7128,7 +7126,7 @@
     </row>
     <row r="41" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="146" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
       <c r="B41" s="146"/>
       <c r="C41" s="146"/>
@@ -7208,7 +7206,7 @@
     </row>
     <row r="43" spans="1:36" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -7248,7 +7246,7 @@
     </row>
     <row r="44" spans="1:36" s="28" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A44" s="138" t="str">
-        <f>'Данные объект'!C18</f>
+        <f>IF('Данные объект'!C18="","",'Данные объект'!C18)</f>
       </c>
       <c r="B44" s="138"/>
       <c r="C44" s="138"/>
@@ -7288,7 +7286,7 @@
     </row>
     <row r="45" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="140"/>
       <c r="C45" s="140"/>
@@ -7368,7 +7366,7 @@
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="138" t="str">
-        <f>'Данные объект'!$C$36</f>
+        <f>IF('Данные объект'!$C$36="","",'Данные объект'!$C$36)</f>
       </c>
       <c r="B47" s="138"/>
       <c r="C47" s="138"/>
@@ -7448,7 +7446,7 @@
     </row>
     <row r="49" spans="1:36" s="20" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" s="143"/>
       <c r="C49" s="143"/>
@@ -7526,7 +7524,7 @@
     </row>
     <row r="51" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" s="140"/>
       <c r="C51" s="140"/>
@@ -7566,7 +7564,7 @@
     </row>
     <row r="52" spans="1:36" s="20" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="143"/>
@@ -7722,7 +7720,7 @@
     </row>
     <row r="56" spans="1:36" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="139"/>
       <c r="C56" s="139"/>
@@ -7767,7 +7765,7 @@
     </row>
     <row r="58" spans="1:36" s="20" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="134" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B58" s="134"/>
       <c r="C58" s="134"/>
@@ -7952,7 +7950,7 @@
     </row>
     <row r="65" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="138" t="str">
-        <f>'Данные объект'!B43</f>
+        <f>IF('Данные объект'!B43="","",'Данные объект'!B43)</f>
       </c>
       <c r="B65" s="138"/>
       <c r="C65" s="138"/>
@@ -8032,7 +8030,7 @@
     </row>
     <row r="67" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L67" s="170"/>
       <c r="M67" s="170"/>
@@ -8073,7 +8071,7 @@
       <c r="J68" s="9"/>
       <c r="K68" s="9"/>
       <c r="L68" s="140" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M68" s="140"/>
       <c r="N68" s="140"/>
@@ -8140,7 +8138,7 @@
     </row>
     <row r="70" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="139" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B70" s="140"/>
       <c r="C70" s="140"/>
@@ -8217,7 +8215,7 @@
       </c>
       <c r="E72" s="31"/>
       <c r="F72" s="31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G72" s="61"/>
       <c r="H72" s="61"/>
@@ -8418,7 +8416,7 @@
       <c r="M77" s="35"/>
       <c r="N77" s="35"/>
       <c r="P77" s="142">
-        <f>'Данные объект'!B6</f>
+        <f>IF('Данные объект'!B6="","",'Данные объект'!B6)</f>
       </c>
       <c r="Q77" s="142"/>
       <c r="R77" s="142"/>
@@ -8443,7 +8441,7 @@
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
       <c r="P78" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="Q78" s="142"/>
       <c r="R78" s="142"/>
@@ -8472,7 +8470,7 @@
     </row>
     <row r="81" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B81" s="149"/>
       <c r="C81" s="149"/>
@@ -8590,7 +8588,7 @@
     </row>
     <row r="84" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="139" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B84" s="140"/>
       <c r="C84" s="140"/>
@@ -8754,7 +8752,7 @@
     </row>
     <row r="90" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H90" s="134"/>
       <c r="I90" s="134"/>
@@ -8770,10 +8768,10 @@
     </row>
     <row r="93" spans="1:36" s="63" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B93" s="31" t="str">
-        <f>F72</f>
+        <f>IF(F72="","",F72)</f>
       </c>
       <c r="C93" s="31"/>
       <c r="D93" s="31"/>
@@ -8792,10 +8790,10 @@
       <c r="Q93" s="31"/>
       <c r="R93" s="31"/>
       <c r="S93" s="31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T93" s="31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U93" s="31"/>
       <c r="V93" s="31"/>
@@ -8904,7 +8902,7 @@
     </row>
     <row r="98" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="134" t="str">
-        <f>'Данные объект'!B33</f>
+        <f>IF('Данные объект'!B33="","",'Данные объект'!B33)</f>
       </c>
       <c r="B98" s="134"/>
       <c r="C98" s="134"/>
@@ -8991,7 +8989,7 @@
     </row>
     <row r="101" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="134" t="str">
-        <f>'Данные объект'!B20</f>
+        <f>IF('Данные объект'!B20="","",'Данные объект'!B20)</f>
       </c>
       <c r="B101" s="134"/>
       <c r="C101" s="134"/>
@@ -9083,7 +9081,7 @@
     </row>
     <row r="105" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="134" t="str">
-        <f>'Данные объект'!B17</f>
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
       </c>
       <c r="B105" s="134"/>
       <c r="C105" s="134"/>
@@ -9205,7 +9203,7 @@
     </row>
     <row r="108" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="134" t="str">
-        <f>'Данные объект'!$B$36</f>
+        <f>IF('Данные объект'!$B$36="","",'Данные объект'!$B$36)</f>
       </c>
       <c r="B108" s="134"/>
       <c r="C108" s="134"/>
@@ -9287,7 +9285,7 @@
     </row>
     <row r="110" spans="1:36" s="20" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B110" s="143"/>
       <c r="C110" s="143"/>
@@ -9407,7 +9405,7 @@
     </row>
     <row r="113" spans="1:36" s="20" customFormat="1" ht="40.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B113" s="143"/>
       <c r="C113" s="143"/>
@@ -9446,9 +9444,7 @@
       <c r="AJ113" s="143"/>
     </row>
     <row r="114" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="134" t="str">
-        <f>[1]Данные!B17</f>
-      </c>
+      <c r="A114" s="134"/>
       <c r="B114" s="134"/>
       <c r="C114" s="134"/>
       <c r="D114" s="134"/>
@@ -9657,7 +9653,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="39"/>
@@ -9670,7 +9666,7 @@
     </row>
     <row r="2" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="43"/>
@@ -9683,7 +9679,7 @@
     </row>
     <row r="3" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="46"/>
@@ -9696,7 +9692,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="42"/>
       <c r="C4" s="43"/>
@@ -9720,7 +9716,7 @@
     </row>
     <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="43"/>
@@ -9733,7 +9729,7 @@
     </row>
     <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7" s="45"/>
       <c r="C7" s="46"/>
@@ -9746,7 +9742,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8" s="85"/>
       <c r="C8" s="43"/>
@@ -9759,7 +9755,7 @@
     </row>
     <row r="9" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" s="86"/>
       <c r="C9" s="46"/>
@@ -9772,7 +9768,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" s="85"/>
       <c r="C10" s="43"/>
@@ -9785,7 +9781,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B11" s="45"/>
       <c r="C11" s="46"/>
@@ -9798,7 +9794,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="42"/>
       <c r="C12" s="43"/>
@@ -9866,7 +9862,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="45"/>
       <c r="C18" s="46"/>
@@ -9879,7 +9875,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="43"/>
@@ -9892,7 +9888,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" s="45"/>
       <c r="C20" s="46"/>
@@ -9916,117 +9912,117 @@
     </row>
     <row r="23" spans="1:9" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B23" s="49"/>
       <c r="C23" s="50" t="str">
-        <f>CONCATENATE(C2,",",C3)</f>
+        <f>IF(COUNTA(C2,C3)=0,"",CONCATENATE(C2,",",C3))</f>
       </c>
       <c r="D23" s="50" t="str">
-        <f>CONCATENATE(D2,",",D3)</f>
+        <f>IF(COUNTA(D2,D3)=0,"",CONCATENATE(D2,",",D3))</f>
       </c>
       <c r="E23" s="51"/>
       <c r="G23" s="52" t="str">
-        <f>CONCATENATE(G8," ",G1,"-",G10," .",G9)</f>
+        <f>IF(COUNTA(G8,G1,G10,G9)=0,"",CONCATENATE(G8," ",G1,"-",G10," .",G9))</f>
       </c>
       <c r="H23" s="52" t="str">
-        <f>CONCATENATE(H8," ",G1,"-",H10,".",H9)</f>
+        <f>IF(COUNTA(H8,G1,H10,H9)=0,"",CONCATENATE(H8," ",G1,"-",H10,".",H9))</f>
       </c>
       <c r="I23" s="52" t="str">
-        <f>CONCATENATE(I8," ",G1,"-",I10," .",I9)</f>
+        <f>IF(COUNTA(I8,G1,I10,I9)=0,"",CONCATENATE(I8," ",G1,"-",I10," .",I9))</f>
       </c>
     </row>
     <row r="24" spans="1:9" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A24" s="49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" s="49"/>
       <c r="C24" s="50" t="str">
-        <f>CONCATENATE(C1,",",C2,",",C3)</f>
+        <f>IF(COUNTA(C1,C2,C3)=0,"",CONCATENATE(C1,",",C2,",",C3))</f>
       </c>
       <c r="D24" s="50" t="str">
-        <f>CONCATENATE(D1,",",D2,",",D3)</f>
+        <f>IF(COUNTA(D1,D2,D3)=0,"",CONCATENATE(D1,",",D2,",",D3))</f>
       </c>
       <c r="E24" s="51"/>
       <c r="G24" s="52" t="str">
-        <f>CONCATENATE(G8," ",G1,"-",G10)</f>
+        <f>IF(COUNTA(G8,G1,G10)=0,"",CONCATENATE(G8," ",G1,"-",G10))</f>
       </c>
       <c r="H24" s="52" t="str">
-        <f>CONCATENATE(H8," ",G1,"-",H10)</f>
+        <f>IF(COUNTA(H8,G1,H10)=0,"",CONCATENATE(H8," ",G1,"-",H10))</f>
       </c>
       <c r="I24" s="52" t="str">
-        <f>CONCATENATE(I8," ",G1,"-",I10)</f>
+        <f>IF(COUNTA(I8,G1,I10)=0,"",CONCATENATE(I8," ",G1,"-",I10))</f>
       </c>
     </row>
     <row r="25" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="C25" s="53" t="str">
-        <f>CONCATENATE(C8," ",C1,"-",C10,".",C9)</f>
+        <f>IF(COUNTA(C8,C1,C10,C9)=0,"",CONCATENATE(C8," ",C1,"-",C10,".",C9))</f>
       </c>
       <c r="D25" s="53" t="str">
-        <f>CONCATENATE(D8," ",D1,"-",D10,".",D9)</f>
+        <f>IF(COUNTA(D8,D1,D10,D9)=0,"",CONCATENATE(D8," ",D1,"-",D10,".",D9))</f>
       </c>
       <c r="E25" s="54"/>
       <c r="G25" s="52" t="str">
-        <f>CONCATENATE(G8," ",G1)</f>
+        <f>IF(COUNTA(G8,G1)=0,"",CONCATENATE(G8," ",G1))</f>
       </c>
       <c r="H25" s="52" t="str">
-        <f>CONCATENATE(H8," ",G1)</f>
+        <f>IF(COUNTA(H8,G1)=0,"",CONCATENATE(H8," ",G1))</f>
       </c>
       <c r="I25" s="52" t="str">
-        <f>CONCATENATE(I8," ",G1)</f>
+        <f>IF(COUNTA(I8,G1)=0,"",CONCATENATE(I8," ",G1))</f>
       </c>
     </row>
     <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C26" s="53" t="str">
-        <f>CONCATENATE(C8," ",C1)</f>
+        <f>IF(COUNTA(C8,C1)=0,"",CONCATENATE(C8," ",C1))</f>
       </c>
       <c r="D26" s="53" t="str">
-        <f>CONCATENATE(D8," ",D1)</f>
+        <f>IF(COUNTA(D8,D1)=0,"",CONCATENATE(D8," ",D1))</f>
       </c>
       <c r="E26" s="54"/>
       <c r="G26" s="49" t="str">
-        <f>CONCATENATE(G6," ",G1," ",G7)</f>
+        <f>IF(COUNTA(G6,G1,G7)=0,"",CONCATENATE(G6," ",G1," ",G7))</f>
       </c>
       <c r="H26" s="49"/>
       <c r="I26" s="49" t="str">
-        <f>CONCATENATE(I6," ",G1," ",I7)</f>
+        <f>IF(COUNTA(I6,G1,I7)=0,"",CONCATENATE(I6," ",G1," ",I7))</f>
       </c>
     </row>
     <row r="27" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
       <c r="C27" s="55" t="str">
-        <f>CONCATENATE(C18," ",C1,"-",C20,".",C19)</f>
+        <f>IF(COUNTA(C18,C1,C20,C19)=0,"",CONCATENATE(C18," ",C1,"-",C20,".",C19))</f>
       </c>
       <c r="D27" s="55" t="str">
-        <f>CONCATENATE(D18," ",D1,"-",D20,".",D19)</f>
+        <f>IF(COUNTA(D18,D1,D20,D19)=0,"",CONCATENATE(D18," ",D1,"-",D20,".",D19))</f>
       </c>
       <c r="E27" s="52"/>
       <c r="G27" s="56" t="str">
-        <f>CONCATENATE(G14," ",G1," ",G15)</f>
+        <f>IF(COUNTA(G14,G1,G15)=0,"",CONCATENATE(G14," ",G1," ",G15))</f>
       </c>
       <c r="H27" s="56"/>
       <c r="I27" s="56" t="str">
-        <f>CONCATENATE(I14," ",G1," ",I15)</f>
+        <f>IF(COUNTA(I14,G1,I15)=0,"",CONCATENATE(I14," ",G1," ",I15))</f>
       </c>
     </row>
     <row r="28" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C28" s="55" t="str">
-        <f>CONCATENATE(C18," ",C1," ",C20)</f>
+        <f>IF(COUNTA(C18,C1,C20)=0,"",CONCATENATE(C18," ",C1," ",C20))</f>
       </c>
       <c r="D28" s="55" t="str">
-        <f>CONCATENATE(D18," ",D1,"-",D20)</f>
+        <f>IF(COUNTA(D18,D1,D20)=0,"",CONCATENATE(D18," ",D1,"-",D20))</f>
       </c>
       <c r="E28" s="52"/>
       <c r="G28" s="49" t="str">
-        <f>CONCATENATE(G16," ",G1," ",G17)</f>
+        <f>IF(COUNTA(G16,G1,G17)=0,"",CONCATENATE(G16," ",G1," ",G17))</f>
       </c>
       <c r="H28" s="49"/>
     </row>
     <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C29" s="57" t="str">
-        <f>CONCATENATE(C18," ",C1)</f>
+        <f>IF(COUNTA(C18,C1)=0,"",CONCATENATE(C18," ",C1))</f>
       </c>
       <c r="D29" s="55" t="str">
-        <f>CONCATENATE(D18," ",D1)</f>
+        <f>IF(COUNTA(D18,D1)=0,"",CONCATENATE(D18," ",D1))</f>
       </c>
       <c r="E29" s="52"/>
     </row>
@@ -10061,50 +10057,50 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="129" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B1" s="130"/>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="66" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="67" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="95"/>
     </row>
     <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B4" s="96"/>
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="96"/>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" s="99"/>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="99"/>
       <c r="C7" s="69"/>
     </row>
     <row r="8" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="129" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="130"/>
     </row>
@@ -10116,265 +10112,265 @@
     </row>
     <row r="10" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="129" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="130"/>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B11" s="71"/>
       <c r="C11" s="72" t="str">
-        <f>CONCATENATE(B11," ",B12," ",B13)</f>
+        <f>IF(COUNTA(B11,B12,B13)=0,"",CONCATENATE(B11," ",B12," ",B13))</f>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="68" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B12" s="71"/>
       <c r="C12" s="72"/>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="71"/>
       <c r="C13" s="72"/>
     </row>
     <row r="14" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="71"/>
       <c r="C14" s="72"/>
     </row>
     <row r="15" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="68" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" s="71"/>
       <c r="C15" s="72" t="str">
-        <f>CONCATENATE(B14," ",B11," ",B15)</f>
+        <f>IF(COUNTA(B14,B11,B15)=0,"",CONCATENATE(B14," ",B11," ",B15))</f>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="71"/>
       <c r="C16" s="72" t="str">
-        <f>CONCATENATE(B16," ",B11)</f>
+        <f>IF(COUNTA(B16,B11)=0,"",CONCATENATE(B16," ",B11))</f>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="71"/>
       <c r="C17" s="73" t="str">
-        <f>CONCATENATE(B16," ",B11," ",B17)</f>
+        <f>IF(COUNTA(B16,B11,B17)=0,"",CONCATENATE(B16," ",B11," ",B17))</f>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" s="71"/>
       <c r="C18" s="73" t="str">
-        <f>CONCATENATE(B16," ",B11," ",B17,".",B18)</f>
+        <f>IF(COUNTA(B16,B11,B17,B18)=0,"",CONCATENATE(B16," ",B11," ",B17,".",B18))</f>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="71"/>
       <c r="C19" s="72" t="str">
-        <f>CONCATENATE(B19," ",B11)</f>
+        <f>IF(COUNTA(B19,B11)=0,"",CONCATENATE(B19," ",B11))</f>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="71"/>
       <c r="C20" s="73" t="str">
-        <f>CONCATENATE(B19," ",B11," ",B20)</f>
+        <f>IF(COUNTA(B19,B11,B20)=0,"",CONCATENATE(B19," ",B11," ",B20))</f>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="74" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B21" s="71"/>
       <c r="C21" s="73" t="str">
-        <f>CONCATENATE(B19," ",B11," ",B20,".",B21)</f>
+        <f>IF(COUNTA(B19,B11,B20,B21)=0,"",CONCATENATE(B19," ",B11," ",B20,".",B21))</f>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="131" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="132"/>
     </row>
     <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="75"/>
       <c r="C23" t="str">
-        <f>CONCATENATE(B23," ",B24,",",B25)</f>
+        <f>IF(COUNTA(B23,B24,B25)=0,"",CONCATENATE(B23," ",B24,",",B25))</f>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="74" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B24" s="92"/>
     </row>
     <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="92"/>
     </row>
     <row r="26" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="76"/>
       <c r="C26" t="str">
-        <f>CONCATENATE(B26," ",B23)</f>
+        <f>IF(COUNTA(B26,B23)=0,"",CONCATENATE(B26," ",B23))</f>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="75"/>
       <c r="C27" t="str">
-        <f>CONCATENATE(B26," ",B23," ",B27)</f>
+        <f>IF(COUNTA(B26,B23,B27)=0,"",CONCATENATE(B26," ",B23," ",B27))</f>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="75"/>
       <c r="C28" t="str">
-        <f>CONCATENATE(B28," ",B23)</f>
+        <f>IF(COUNTA(B28,B23)=0,"",CONCATENATE(B28," ",B23))</f>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="75"/>
       <c r="C29" t="str">
-        <f>CONCATENATE(B28," ",B23," ",B29)</f>
+        <f>IF(COUNTA(B28,B23,B29)=0,"",CONCATENATE(B28," ",B23," ",B29))</f>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" s="75"/>
       <c r="C30" t="str">
-        <f>CONCATENATE(B30," ",B23)</f>
+        <f>IF(COUNTA(B30,B23)=0,"",CONCATENATE(B30," ",B23))</f>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" s="75"/>
       <c r="C31" t="str">
-        <f>CONCATENATE(B30," ",B23," ",B31)</f>
+        <f>IF(COUNTA(B30,B23,B31)=0,"",CONCATENATE(B30," ",B23," ",B31))</f>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B32" s="75"/>
       <c r="C32" t="str">
-        <f>CONCATENATE(B32," ",B23)</f>
+        <f>IF(COUNTA(B32,B23)=0,"",CONCATENATE(B32," ",B23))</f>
       </c>
     </row>
     <row r="33" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="75"/>
       <c r="C33" s="77" t="str">
-        <f>CONCATENATE(B32," ",B23," ",B33)</f>
+        <f>IF(COUNTA(B32,B23,B33)=0,"",CONCATENATE(B32," ",B23," ",B33))</f>
       </c>
     </row>
     <row r="34" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="74" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B34" s="93"/>
       <c r="C34" t="str">
-        <f>CONCATENATE(B32," ",B23," ",B33,", ",B34)</f>
+        <f>IF(COUNTA(B32,B23,B33,B34)=0,"",CONCATENATE(B32," ",B23," ",B33,", ",B34))</f>
       </c>
     </row>
     <row r="35" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="75"/>
       <c r="C35" t="str">
-        <f>CONCATENATE(B35," ",B23)</f>
+        <f>IF(COUNTA(B35,B23)=0,"",CONCATENATE(B35," ",B23))</f>
       </c>
     </row>
     <row r="36" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="75"/>
       <c r="C36" s="77" t="str">
-        <f>CONCATENATE(B35," ",B23," ",B36)</f>
+        <f>IF(COUNTA(B35,B23,B36)=0,"",CONCATENATE(B35," ",B23," ",B36))</f>
       </c>
     </row>
     <row r="37" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="74" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B37" s="75"/>
       <c r="C37" t="str">
-        <f>CONCATENATE(B35," ",B23," ",B36,", ",B37)</f>
+        <f>IF(COUNTA(B35,B23,B36,B37)=0,"",CONCATENATE(B35," ",B23," ",B36,", ",B37))</f>
       </c>
     </row>
     <row r="38" spans="1:31" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="129" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38" s="133"/>
     </row>
     <row r="39" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B39" s="78"/>
     </row>
     <row r="40" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="68" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" s="78"/>
     </row>
     <row r="41" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B41" s="78"/>
     </row>
     <row r="42" spans="1:31" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B42" s="78"/>
     </row>
@@ -10386,10 +10382,10 @@
     </row>
     <row r="44" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="67" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B44" s="78" t="str">
-        <f>B3</f>
+        <f>IF(B3="","",B3)</f>
       </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
@@ -11237,7 +11233,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AJ1" s="21"/>
+      <c r="AJ1" s="21" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" spans="1:43" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AJ2" s="21" t="s">
@@ -11259,7 +11257,7 @@
     </row>
     <row r="4" spans="1:43" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="138" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
@@ -11299,7 +11297,7 @@
     </row>
     <row r="5" spans="1:43" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A5" s="138" t="str">
-        <f>'Данные объект'!B9</f>
+        <f>IF('Данные объект'!B9="","",'Данные объект'!B9)</f>
       </c>
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
@@ -11379,7 +11377,7 @@
     </row>
     <row r="7" spans="1:43" s="20" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="137"/>
       <c r="C7" s="137"/>
@@ -11457,7 +11455,7 @@
     </row>
     <row r="9" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="146" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="B9" s="146"/>
       <c r="C9" s="146"/>
@@ -11497,7 +11495,7 @@
     </row>
     <row r="10" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="140"/>
       <c r="C10" s="140"/>
@@ -11537,7 +11535,7 @@
     </row>
     <row r="11" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="146" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="B11" s="146"/>
       <c r="C11" s="146"/>
@@ -11577,7 +11575,7 @@
     </row>
     <row r="12" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="140"/>
       <c r="C12" s="140"/>
@@ -11617,7 +11615,7 @@
     </row>
     <row r="13" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="146" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="B13" s="146"/>
       <c r="C13" s="146"/>
@@ -11657,7 +11655,7 @@
     </row>
     <row r="14" spans="1:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="140"/>
       <c r="C14" s="140"/>
@@ -11702,7 +11700,7 @@
     </row>
     <row r="16" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="146" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B16" s="146"/>
       <c r="C16" s="146"/>
@@ -11782,7 +11780,7 @@
     </row>
     <row r="18" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B18" s="146"/>
       <c r="C18" s="146"/>
@@ -11822,7 +11820,7 @@
     </row>
     <row r="19" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="140"/>
       <c r="C19" s="140"/>
@@ -11862,7 +11860,7 @@
     </row>
     <row r="20" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B20" s="146"/>
       <c r="C20" s="146"/>
@@ -11902,7 +11900,7 @@
     </row>
     <row r="21" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="140"/>
       <c r="C21" s="140"/>
@@ -11947,7 +11945,7 @@
     </row>
     <row r="23" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="146" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="B23" s="146"/>
       <c r="C23" s="146"/>
@@ -12027,7 +12025,7 @@
     </row>
     <row r="25" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B25" s="146"/>
       <c r="C25" s="146"/>
@@ -12067,7 +12065,7 @@
     </row>
     <row r="26" spans="1:36" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="140"/>
       <c r="C26" s="140"/>
@@ -12107,7 +12105,7 @@
     </row>
     <row r="27" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B27" s="146"/>
       <c r="C27" s="146"/>
@@ -12147,7 +12145,7 @@
     </row>
     <row r="28" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" s="140"/>
       <c r="C28" s="140"/>
@@ -12299,9 +12297,7 @@
       <c r="B33" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="134">
-        <v>1</v>
-      </c>
+      <c r="C33" s="134"/>
       <c r="D33" s="134"/>
       <c r="E33" s="154" t="s">
         <v>157</v>
@@ -12315,7 +12311,7 @@
       <c r="Y33" s="35"/>
       <c r="Z33" s="35"/>
       <c r="AB33" s="142">
-        <f>P79</f>
+        <f>IF(P79="","",P79)</f>
       </c>
       <c r="AC33" s="142"/>
       <c r="AD33" s="142"/>
@@ -12352,7 +12348,7 @@
     </row>
     <row r="36" spans="1:36" s="20" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B36" s="137"/>
       <c r="C36" s="137"/>
@@ -12392,7 +12388,7 @@
     </row>
     <row r="37" spans="1:36" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="138" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="B37" s="138"/>
       <c r="C37" s="138"/>
@@ -12432,7 +12428,7 @@
     </row>
     <row r="38" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B38" s="140"/>
       <c r="C38" s="140"/>
@@ -12472,7 +12468,7 @@
     </row>
     <row r="39" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="138" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="B39" s="138"/>
       <c r="C39" s="138"/>
@@ -12512,7 +12508,7 @@
     </row>
     <row r="40" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" s="151"/>
       <c r="C40" s="151"/>
@@ -12557,7 +12553,7 @@
     </row>
     <row r="42" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="146" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
       <c r="B42" s="146"/>
       <c r="C42" s="146"/>
@@ -12637,7 +12633,7 @@
     </row>
     <row r="44" spans="1:36" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44" s="137"/>
       <c r="C44" s="137"/>
@@ -12677,7 +12673,7 @@
     </row>
     <row r="45" spans="1:36" s="28" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="138" t="str">
-        <f>'Данные объект'!C18</f>
+        <f>IF('Данные объект'!C18="","",'Данные объект'!C18)</f>
       </c>
       <c r="B45" s="138"/>
       <c r="C45" s="138"/>
@@ -12717,7 +12713,7 @@
     </row>
     <row r="46" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" s="140"/>
       <c r="C46" s="140"/>
@@ -12797,7 +12793,7 @@
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="138" t="str">
-        <f>'Данные объект'!$C$36</f>
+        <f>IF('Данные объект'!$C$36="","",'Данные объект'!$C$36)</f>
       </c>
       <c r="B48" s="138"/>
       <c r="C48" s="138"/>
@@ -12877,7 +12873,7 @@
     </row>
     <row r="50" spans="1:36" s="20" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50" s="143"/>
       <c r="C50" s="143"/>
@@ -12955,7 +12951,7 @@
     </row>
     <row r="52" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52" s="140"/>
       <c r="C52" s="140"/>
@@ -12995,7 +12991,7 @@
     </row>
     <row r="53" spans="1:36" s="20" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53" s="143"/>
       <c r="C53" s="143"/>
@@ -13151,7 +13147,7 @@
     </row>
     <row r="57" spans="1:36" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" s="139"/>
       <c r="C57" s="139"/>
@@ -13196,7 +13192,7 @@
     </row>
     <row r="59" spans="1:36" s="20" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="134" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B59" s="134"/>
       <c r="C59" s="134"/>
@@ -13302,7 +13298,7 @@
       <c r="M63" s="147"/>
       <c r="N63" s="147"/>
       <c r="O63" s="87" t="str">
-        <f>A5</f>
+        <f>IF(A5="","",A5)</f>
       </c>
       <c r="P63" s="87"/>
       <c r="Q63" s="87"/>
@@ -13375,7 +13371,7 @@
     </row>
     <row r="66" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="138" t="str">
-        <f>'Данные объект'!B43</f>
+        <f>IF('Данные объект'!B43="","",'Данные объект'!B43)</f>
       </c>
       <c r="B66" s="138"/>
       <c r="C66" s="138"/>
@@ -13458,7 +13454,7 @@
         <v>12</v>
       </c>
       <c r="P68" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q68" s="134"/>
       <c r="R68" s="134"/>
@@ -13498,7 +13494,7 @@
       <c r="N69" s="9"/>
       <c r="O69" s="9"/>
       <c r="P69" s="136" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q69" s="136"/>
       <c r="R69" s="136"/>
@@ -13561,7 +13557,7 @@
     </row>
     <row r="71" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="139" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B71" s="140"/>
       <c r="C71" s="140"/>
@@ -13809,7 +13805,7 @@
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
       <c r="P78" s="142">
-        <f>'Данные объект'!B6</f>
+        <f>IF('Данные объект'!B6="","",'Данные объект'!B6)</f>
       </c>
       <c r="Q78" s="142"/>
       <c r="R78" s="142"/>
@@ -13834,7 +13830,7 @@
       <c r="M79" s="35"/>
       <c r="N79" s="35"/>
       <c r="P79" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="Q79" s="142"/>
       <c r="R79" s="142"/>
@@ -13863,7 +13859,7 @@
     </row>
     <row r="82" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B82" s="149"/>
       <c r="C82" s="149"/>
@@ -13981,7 +13977,7 @@
     </row>
     <row r="85" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="139" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B85" s="140"/>
       <c r="C85" s="140"/>
@@ -14026,7 +14022,7 @@
     </row>
     <row r="87" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="134" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B87" s="134"/>
       <c r="C87" s="134"/>
@@ -14145,7 +14141,7 @@
     </row>
     <row r="91" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H91" s="134"/>
       <c r="I91" s="134"/>
@@ -14161,10 +14157,10 @@
     </row>
     <row r="94" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B94" s="31" t="str">
-        <f>G73</f>
+        <f>IF(G73="","",G73)</f>
       </c>
       <c r="C94" s="31"/>
       <c r="D94" s="31"/>
@@ -14182,10 +14178,10 @@
       <c r="P94" s="31"/>
       <c r="Q94" s="31"/>
       <c r="R94" s="31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S94" s="31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T94" s="31"/>
       <c r="U94" s="31"/>
@@ -14207,10 +14203,10 @@
     </row>
     <row r="95" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B95" s="34">
-        <f>U73</f>
+        <f>IF(U73="","",U73)</f>
       </c>
       <c r="C95" s="34"/>
       <c r="D95" s="34"/>
@@ -14228,10 +14224,10 @@
       <c r="P95" s="34"/>
       <c r="Q95" s="34"/>
       <c r="R95" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S95" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T95" s="34"/>
       <c r="U95" s="34"/>
@@ -14253,10 +14249,10 @@
     </row>
     <row r="96" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B96" s="31">
-        <f>A75</f>
+        <f>IF(A75="","",A75)</f>
       </c>
       <c r="C96" s="31"/>
       <c r="D96" s="31"/>
@@ -14274,10 +14270,10 @@
       <c r="P96" s="31"/>
       <c r="Q96" s="31"/>
       <c r="R96" s="31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S96" s="31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T96" s="31"/>
       <c r="U96" s="31"/>
@@ -14387,7 +14383,7 @@
     </row>
     <row r="101" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="134" t="str">
-        <f>'Данные объект'!B33</f>
+        <f>IF('Данные объект'!B33="","",'Данные объект'!B33)</f>
       </c>
       <c r="B101" s="134"/>
       <c r="C101" s="134"/>
@@ -14474,7 +14470,7 @@
     </row>
     <row r="104" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="134" t="str">
-        <f>'Данные объект'!B20</f>
+        <f>IF('Данные объект'!B20="","",'Данные объект'!B20)</f>
       </c>
       <c r="B104" s="134"/>
       <c r="C104" s="134"/>
@@ -14566,7 +14562,7 @@
     </row>
     <row r="108" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="134" t="str">
-        <f>'Данные объект'!B17</f>
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
       </c>
       <c r="B108" s="134"/>
       <c r="C108" s="134"/>
@@ -14688,7 +14684,7 @@
     </row>
     <row r="111" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="134" t="str">
-        <f>'Данные объект'!$B$36</f>
+        <f>IF('Данные объект'!$B$36="","",'Данные объект'!$B$36)</f>
       </c>
       <c r="B111" s="134"/>
       <c r="C111" s="134"/>
@@ -14770,7 +14766,7 @@
     </row>
     <row r="113" spans="1:36" s="20" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B113" s="143"/>
       <c r="C113" s="143"/>
@@ -14810,7 +14806,7 @@
     </row>
     <row r="114" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="141" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B114" s="141"/>
       <c r="C114" s="141"/>
@@ -14839,7 +14835,7 @@
       <c r="Z114" s="15"/>
       <c r="AA114" s="15"/>
       <c r="AB114" s="141" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC114" s="141"/>
       <c r="AD114" s="141"/>
@@ -14894,7 +14890,7 @@
     </row>
     <row r="116" spans="1:36" s="20" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B116" s="143"/>
       <c r="C116" s="143"/>
@@ -14933,9 +14929,7 @@
       <c r="AJ116" s="143"/>
     </row>
     <row r="117" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="134" t="e">
-        <f>#REF!</f>
-      </c>
+      <c r="A117" s="134"/>
       <c r="B117" s="134"/>
       <c r="C117" s="134"/>
       <c r="D117" s="134"/>
@@ -15144,7 +15138,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AJ1" s="21"/>
+      <c r="AJ1" s="21" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" spans="1:43" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AJ2" s="21" t="s">
@@ -15166,7 +15162,7 @@
     </row>
     <row r="4" spans="1:43" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="138" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
@@ -15206,7 +15202,7 @@
     </row>
     <row r="5" spans="1:43" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A5" s="138" t="str">
-        <f>'Данные объект'!B9</f>
+        <f>IF('Данные объект'!B9="","",'Данные объект'!B9)</f>
       </c>
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
@@ -15286,7 +15282,7 @@
     </row>
     <row r="7" spans="1:43" s="20" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="137"/>
       <c r="C7" s="137"/>
@@ -15364,7 +15360,7 @@
     </row>
     <row r="9" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="146" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="B9" s="146"/>
       <c r="C9" s="146"/>
@@ -15404,7 +15400,7 @@
     </row>
     <row r="10" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="140"/>
       <c r="C10" s="140"/>
@@ -15444,7 +15440,7 @@
     </row>
     <row r="11" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="146" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="B11" s="146"/>
       <c r="C11" s="146"/>
@@ -15484,7 +15480,7 @@
     </row>
     <row r="12" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="140"/>
       <c r="C12" s="140"/>
@@ -15524,7 +15520,7 @@
     </row>
     <row r="13" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="146" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="B13" s="146"/>
       <c r="C13" s="146"/>
@@ -15564,7 +15560,7 @@
     </row>
     <row r="14" spans="1:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="140"/>
       <c r="C14" s="140"/>
@@ -15609,7 +15605,7 @@
     </row>
     <row r="16" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="146" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B16" s="146"/>
       <c r="C16" s="146"/>
@@ -15689,7 +15685,7 @@
     </row>
     <row r="18" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B18" s="146"/>
       <c r="C18" s="146"/>
@@ -15729,7 +15725,7 @@
     </row>
     <row r="19" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="140"/>
       <c r="C19" s="140"/>
@@ -15769,7 +15765,7 @@
     </row>
     <row r="20" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B20" s="146"/>
       <c r="C20" s="146"/>
@@ -15809,7 +15805,7 @@
     </row>
     <row r="21" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="140"/>
       <c r="C21" s="140"/>
@@ -15854,7 +15850,7 @@
     </row>
     <row r="23" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="146" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="B23" s="146"/>
       <c r="C23" s="146"/>
@@ -15934,7 +15930,7 @@
     </row>
     <row r="25" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B25" s="146"/>
       <c r="C25" s="146"/>
@@ -15974,7 +15970,7 @@
     </row>
     <row r="26" spans="1:36" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="140"/>
       <c r="C26" s="140"/>
@@ -16014,7 +16010,7 @@
     </row>
     <row r="27" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B27" s="146"/>
       <c r="C27" s="146"/>
@@ -16054,7 +16050,7 @@
     </row>
     <row r="28" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" s="140"/>
       <c r="C28" s="140"/>
@@ -16207,11 +16203,11 @@
         <v>18</v>
       </c>
       <c r="C33" s="134">
-        <f>'АОСР-1'!C33+1</f>
+        <f>IF('АОСР-1'!C33="","",'АОСР-1'!C33+1)</f>
       </c>
       <c r="D33" s="134"/>
       <c r="E33" s="134" t="str">
-        <f>'АОСР-1'!E33</f>
+        <f>IF('АОСР-1'!E33="","",'АОСР-1'!E33)</f>
       </c>
       <c r="F33" s="134"/>
       <c r="G33" s="134"/>
@@ -16222,7 +16218,7 @@
       <c r="Y33" s="35"/>
       <c r="Z33" s="35"/>
       <c r="AB33" s="142">
-        <f>P79</f>
+        <f>IF(P79="","",P79)</f>
       </c>
       <c r="AC33" s="142"/>
       <c r="AD33" s="142"/>
@@ -16259,7 +16255,7 @@
     </row>
     <row r="36" spans="1:36" s="20" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B36" s="137"/>
       <c r="C36" s="137"/>
@@ -16299,7 +16295,7 @@
     </row>
     <row r="37" spans="1:36" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="138" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="B37" s="138"/>
       <c r="C37" s="138"/>
@@ -16339,7 +16335,7 @@
     </row>
     <row r="38" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B38" s="140"/>
       <c r="C38" s="140"/>
@@ -16379,7 +16375,7 @@
     </row>
     <row r="39" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="138" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="B39" s="138"/>
       <c r="C39" s="138"/>
@@ -16419,7 +16415,7 @@
     </row>
     <row r="40" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" s="151"/>
       <c r="C40" s="151"/>
@@ -16464,7 +16460,7 @@
     </row>
     <row r="42" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="146" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
       <c r="B42" s="146"/>
       <c r="C42" s="146"/>
@@ -16544,7 +16540,7 @@
     </row>
     <row r="44" spans="1:36" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44" s="137"/>
       <c r="C44" s="137"/>
@@ -16584,7 +16580,7 @@
     </row>
     <row r="45" spans="1:36" s="28" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="138" t="str">
-        <f>'Данные объект'!C18</f>
+        <f>IF('Данные объект'!C18="","",'Данные объект'!C18)</f>
       </c>
       <c r="B45" s="138"/>
       <c r="C45" s="138"/>
@@ -16624,7 +16620,7 @@
     </row>
     <row r="46" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" s="140"/>
       <c r="C46" s="140"/>
@@ -16704,7 +16700,7 @@
     </row>
     <row r="48" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="138" t="str">
-        <f>'Данные объект'!$C$36</f>
+        <f>IF('Данные объект'!$C$36="","",'Данные объект'!$C$36)</f>
       </c>
       <c r="B48" s="138"/>
       <c r="C48" s="138"/>
@@ -16784,7 +16780,7 @@
     </row>
     <row r="50" spans="1:36" s="20" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50" s="143"/>
       <c r="C50" s="143"/>
@@ -16862,7 +16858,7 @@
     </row>
     <row r="52" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52" s="140"/>
       <c r="C52" s="140"/>
@@ -16902,7 +16898,7 @@
     </row>
     <row r="53" spans="1:36" s="20" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53" s="143"/>
       <c r="C53" s="143"/>
@@ -17058,7 +17054,7 @@
     </row>
     <row r="57" spans="1:36" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" s="139"/>
       <c r="C57" s="139"/>
@@ -17103,7 +17099,7 @@
     </row>
     <row r="59" spans="1:36" s="20" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="134" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B59" s="134"/>
       <c r="C59" s="134"/>
@@ -17203,7 +17199,7 @@
       <c r="G63" s="87"/>
       <c r="H63" s="87"/>
       <c r="I63" s="156" t="str">
-        <f>'АОСР-1'!O63</f>
+        <f>IF('АОСР-1'!O63="","",'АОСР-1'!O63)</f>
       </c>
       <c r="J63" s="156"/>
       <c r="K63" s="156"/>
@@ -17213,9 +17209,7 @@
       <c r="M63" s="87"/>
       <c r="N63" s="87"/>
       <c r="O63" s="87"/>
-      <c r="P63" s="157">
-        <v>4</v>
-      </c>
+      <c r="P63" s="157"/>
       <c r="Q63" s="157"/>
       <c r="R63" s="157"/>
       <c r="S63" s="103" t="s">
@@ -17225,9 +17219,7 @@
       <c r="U63" s="105" t="s">
         <v>165</v>
       </c>
-      <c r="V63" s="105">
-        <v>7</v>
-      </c>
+      <c r="V63" s="105"/>
       <c r="W63" s="161" t="s">
         <v>148</v>
       </c>
@@ -17327,7 +17319,7 @@
     </row>
     <row r="66" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="156" t="str">
-        <f>'Данные объект'!B43</f>
+        <f>IF('Данные объект'!B43="","",'Данные объект'!B43)</f>
       </c>
       <c r="B66" s="156"/>
       <c r="C66" s="156"/>
@@ -17462,7 +17454,7 @@
       <c r="N69" s="90"/>
       <c r="O69" s="90"/>
       <c r="P69" s="160" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q69" s="160"/>
       <c r="R69" s="160"/>
@@ -17487,7 +17479,7 @@
     </row>
     <row r="70" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="155" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B70" s="155"/>
       <c r="C70" s="155"/>
@@ -17497,15 +17489,15 @@
       <c r="E70" s="157"/>
       <c r="F70" s="157"/>
       <c r="G70" s="88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H70" s="156">
-        <f>V63</f>
+        <f>IF(V63="","",V63)</f>
       </c>
       <c r="I70" s="156"/>
       <c r="J70" s="156"/>
       <c r="K70" s="119" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L70" s="91" t="s">
         <v>155</v>
@@ -17537,7 +17529,7 @@
     </row>
     <row r="71" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="158" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B71" s="159"/>
       <c r="C71" s="159"/>
@@ -17585,7 +17577,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="134" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H73" s="134"/>
       <c r="I73" s="134"/>
@@ -17600,7 +17592,7 @@
       <c r="R73" s="134"/>
       <c r="S73" s="134"/>
       <c r="T73" s="31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U73" s="134"/>
       <c r="V73" s="134"/>
@@ -17787,7 +17779,7 @@
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
       <c r="P78" s="142">
-        <f>'Данные объект'!B6</f>
+        <f>IF('Данные объект'!B6="","",'Данные объект'!B6)</f>
       </c>
       <c r="Q78" s="142"/>
       <c r="R78" s="142"/>
@@ -17812,7 +17804,7 @@
       <c r="M79" s="35"/>
       <c r="N79" s="35"/>
       <c r="P79" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="Q79" s="142"/>
       <c r="R79" s="142"/>
@@ -17841,7 +17833,7 @@
     </row>
     <row r="82" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B82" s="149"/>
       <c r="C82" s="149"/>
@@ -17959,7 +17951,7 @@
     </row>
     <row r="85" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="139" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B85" s="140"/>
       <c r="C85" s="140"/>
@@ -18004,7 +17996,7 @@
     </row>
     <row r="87" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="134" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B87" s="134"/>
       <c r="C87" s="134"/>
@@ -18123,7 +18115,7 @@
     </row>
     <row r="91" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H91" s="134"/>
       <c r="I91" s="134"/>
@@ -18139,10 +18131,10 @@
     </row>
     <row r="94" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B94" s="31" t="str">
-        <f>G73</f>
+        <f>IF(G73="","",G73)</f>
       </c>
       <c r="C94" s="31"/>
       <c r="D94" s="31"/>
@@ -18160,10 +18152,10 @@
       <c r="P94" s="31"/>
       <c r="Q94" s="31"/>
       <c r="R94" s="31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S94" s="31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T94" s="31"/>
       <c r="U94" s="31"/>
@@ -18185,10 +18177,10 @@
     </row>
     <row r="95" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B95" s="34">
-        <f>U73</f>
+        <f>IF(U73="","",U73)</f>
       </c>
       <c r="C95" s="34"/>
       <c r="D95" s="34"/>
@@ -18206,10 +18198,10 @@
       <c r="P95" s="34"/>
       <c r="Q95" s="34"/>
       <c r="R95" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S95" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T95" s="34"/>
       <c r="U95" s="34"/>
@@ -18231,10 +18223,10 @@
     </row>
     <row r="96" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B96" s="37" t="str">
-        <f>M70</f>
+        <f>IF(M70="","",M70)</f>
       </c>
       <c r="C96" s="37"/>
       <c r="D96" s="37"/>
@@ -18252,10 +18244,10 @@
       <c r="P96" s="37"/>
       <c r="Q96" s="34"/>
       <c r="R96" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S96" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T96" s="34"/>
       <c r="U96" s="34"/>
@@ -18277,7 +18269,7 @@
     </row>
     <row r="97" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B97" s="37"/>
       <c r="C97" s="37"/>
@@ -18296,10 +18288,10 @@
       <c r="P97" s="37"/>
       <c r="Q97" s="34"/>
       <c r="R97" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S97" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T97" s="34"/>
       <c r="U97" s="34"/>
@@ -18409,7 +18401,7 @@
     </row>
     <row r="102" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="134" t="str">
-        <f>'Данные объект'!B33</f>
+        <f>IF('Данные объект'!B33="","",'Данные объект'!B33)</f>
       </c>
       <c r="B102" s="134"/>
       <c r="C102" s="134"/>
@@ -18496,7 +18488,7 @@
     </row>
     <row r="105" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="134" t="str">
-        <f>'Данные объект'!B20</f>
+        <f>IF('Данные объект'!B20="","",'Данные объект'!B20)</f>
       </c>
       <c r="B105" s="134"/>
       <c r="C105" s="134"/>
@@ -18588,7 +18580,7 @@
     </row>
     <row r="109" spans="1:36" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A109" s="134" t="str">
-        <f>'Данные объект'!B17</f>
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
       </c>
       <c r="B109" s="134"/>
       <c r="C109" s="134"/>
@@ -18710,7 +18702,7 @@
     </row>
     <row r="112" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A112" s="134" t="str">
-        <f>'Данные объект'!$B$36</f>
+        <f>IF('Данные объект'!$B$36="","",'Данные объект'!$B$36)</f>
       </c>
       <c r="B112" s="134"/>
       <c r="C112" s="134"/>
@@ -18792,7 +18784,7 @@
     </row>
     <row r="114" spans="1:36" s="20" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B114" s="143"/>
       <c r="C114" s="143"/>
@@ -18832,7 +18824,7 @@
     </row>
     <row r="115" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B115" s="134"/>
       <c r="C115" s="134"/>
@@ -18861,7 +18853,7 @@
       <c r="Z115" s="35"/>
       <c r="AA115" s="35"/>
       <c r="AB115" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC115" s="134"/>
       <c r="AD115" s="134"/>
@@ -18916,7 +18908,7 @@
     </row>
     <row r="117" spans="1:36" s="20" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B117" s="143"/>
       <c r="C117" s="143"/>
@@ -18955,9 +18947,7 @@
       <c r="AJ117" s="143"/>
     </row>
     <row r="118" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="134" t="e">
-        <f>#REF!</f>
-      </c>
+      <c r="A118" s="134"/>
       <c r="B118" s="134"/>
       <c r="C118" s="134"/>
       <c r="D118" s="134"/>
@@ -19185,7 +19175,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AJ1" s="21"/>
+      <c r="AJ1" s="21" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" spans="1:43" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AJ2" s="21" t="s">
@@ -19207,7 +19199,7 @@
     </row>
     <row r="4" spans="1:43" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="138" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
@@ -19247,7 +19239,7 @@
     </row>
     <row r="5" spans="1:43" s="20" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138" t="str">
-        <f>'Данные объект'!B9</f>
+        <f>IF('Данные объект'!B9="","",'Данные объект'!B9)</f>
       </c>
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
@@ -19327,7 +19319,7 @@
     </row>
     <row r="7" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="137"/>
       <c r="C7" s="137"/>
@@ -19367,7 +19359,7 @@
     </row>
     <row r="8" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="146" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="B8" s="146"/>
       <c r="C8" s="146"/>
@@ -19407,7 +19399,7 @@
     </row>
     <row r="9" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="140"/>
       <c r="C9" s="140"/>
@@ -19447,7 +19439,7 @@
     </row>
     <row r="10" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="146" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="B10" s="146"/>
       <c r="C10" s="146"/>
@@ -19487,7 +19479,7 @@
     </row>
     <row r="11" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="140"/>
       <c r="C11" s="140"/>
@@ -19527,7 +19519,7 @@
     </row>
     <row r="12" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="146" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="B12" s="146"/>
       <c r="C12" s="146"/>
@@ -19567,7 +19559,7 @@
     </row>
     <row r="13" spans="1:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="140"/>
       <c r="C13" s="140"/>
@@ -19612,7 +19604,7 @@
     </row>
     <row r="15" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="146" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B15" s="146"/>
       <c r="C15" s="146"/>
@@ -19692,7 +19684,7 @@
     </row>
     <row r="17" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B17" s="146"/>
       <c r="C17" s="146"/>
@@ -19732,7 +19724,7 @@
     </row>
     <row r="18" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="140"/>
       <c r="C18" s="140"/>
@@ -19772,7 +19764,7 @@
     </row>
     <row r="19" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B19" s="146"/>
       <c r="C19" s="146"/>
@@ -19812,7 +19804,7 @@
     </row>
     <row r="20" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="140"/>
       <c r="C20" s="140"/>
@@ -19857,7 +19849,7 @@
     </row>
     <row r="22" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="146" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="B22" s="146"/>
       <c r="C22" s="146"/>
@@ -19937,7 +19929,7 @@
     </row>
     <row r="24" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B24" s="146"/>
       <c r="C24" s="146"/>
@@ -19977,7 +19969,7 @@
     </row>
     <row r="25" spans="1:36" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="140"/>
       <c r="C25" s="140"/>
@@ -20017,7 +20009,7 @@
     </row>
     <row r="26" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B26" s="146"/>
       <c r="C26" s="146"/>
@@ -20057,7 +20049,7 @@
     </row>
     <row r="27" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" s="140"/>
       <c r="C27" s="140"/>
@@ -20210,11 +20202,11 @@
         <v>18</v>
       </c>
       <c r="C32" s="134">
-        <f>'АОСР-2'!C33:D33+1</f>
+        <f>IF('АОСР-2'!C33="","",'АОСР-2'!C33+1)</f>
       </c>
       <c r="D32" s="134"/>
       <c r="E32" s="134" t="str">
-        <f>'АОСР-1'!E33</f>
+        <f>IF('АОСР-1'!E33="","",'АОСР-1'!E33)</f>
       </c>
       <c r="F32" s="134"/>
       <c r="G32" s="134"/>
@@ -20225,7 +20217,7 @@
       <c r="Y32" s="35"/>
       <c r="Z32" s="35"/>
       <c r="AB32" s="142">
-        <f>P78</f>
+        <f>IF(P78="","",P78)</f>
       </c>
       <c r="AC32" s="142"/>
       <c r="AD32" s="142"/>
@@ -20262,7 +20254,7 @@
     </row>
     <row r="35" spans="1:36" s="20" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="137"/>
       <c r="C35" s="137"/>
@@ -20302,7 +20294,7 @@
     </row>
     <row r="36" spans="1:36" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="138" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="B36" s="138"/>
       <c r="C36" s="138"/>
@@ -20342,7 +20334,7 @@
     </row>
     <row r="37" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B37" s="140"/>
       <c r="C37" s="140"/>
@@ -20382,7 +20374,7 @@
     </row>
     <row r="38" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="138" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -20422,7 +20414,7 @@
     </row>
     <row r="39" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="151"/>
@@ -20467,7 +20459,7 @@
     </row>
     <row r="41" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="146" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
       <c r="B41" s="146"/>
       <c r="C41" s="146"/>
@@ -20547,7 +20539,7 @@
     </row>
     <row r="43" spans="1:36" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -20587,7 +20579,7 @@
     </row>
     <row r="44" spans="1:36" s="28" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="138" t="str">
-        <f>'Данные объект'!C18</f>
+        <f>IF('Данные объект'!C18="","",'Данные объект'!C18)</f>
       </c>
       <c r="B44" s="138"/>
       <c r="C44" s="138"/>
@@ -20627,7 +20619,7 @@
     </row>
     <row r="45" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="140"/>
       <c r="C45" s="140"/>
@@ -20707,7 +20699,7 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="138" t="str">
-        <f>'Данные объект'!$C$36</f>
+        <f>IF('Данные объект'!$C$36="","",'Данные объект'!$C$36)</f>
       </c>
       <c r="B47" s="138"/>
       <c r="C47" s="138"/>
@@ -20787,7 +20779,7 @@
     </row>
     <row r="49" spans="1:36" s="20" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" s="143"/>
       <c r="C49" s="143"/>
@@ -20865,7 +20857,7 @@
     </row>
     <row r="51" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" s="140"/>
       <c r="C51" s="140"/>
@@ -20905,7 +20897,7 @@
     </row>
     <row r="52" spans="1:36" s="20" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="143"/>
@@ -21061,7 +21053,7 @@
     </row>
     <row r="56" spans="1:36" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="139"/>
       <c r="C56" s="139"/>
@@ -21106,7 +21098,7 @@
     </row>
     <row r="58" spans="1:36" s="20" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="134" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B58" s="134"/>
       <c r="C58" s="134"/>
@@ -21210,7 +21202,7 @@
       <c r="K62" s="163"/>
       <c r="L62" s="163"/>
       <c r="M62" s="156" t="str">
-        <f>'АОСР-1'!O63</f>
+        <f>IF('АОСР-1'!O63="","",'АОСР-1'!O63)</f>
       </c>
       <c r="N62" s="156"/>
       <c r="O62" s="156"/>
@@ -21230,9 +21222,7 @@
       <c r="W62" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="X62" s="161">
-        <v>3.6</v>
-      </c>
+      <c r="X62" s="161"/>
       <c r="Y62" s="161"/>
       <c r="Z62" s="161"/>
       <c r="AA62" s="155" t="s">
@@ -21330,7 +21320,7 @@
     </row>
     <row r="65" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="156" t="str">
-        <f>'Данные объект'!B43</f>
+        <f>IF('Данные объект'!B43="","",'Данные объект'!B43)</f>
       </c>
       <c r="B65" s="156"/>
       <c r="C65" s="156"/>
@@ -21451,7 +21441,7 @@
       <c r="N68" s="9"/>
       <c r="O68" s="9"/>
       <c r="P68" s="136" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q68" s="136"/>
       <c r="R68" s="136"/>
@@ -21514,7 +21504,7 @@
     </row>
     <row r="70" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="139" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B70" s="140"/>
       <c r="C70" s="140"/>
@@ -21573,7 +21563,7 @@
       <c r="P72" s="31"/>
       <c r="Q72" s="31"/>
       <c r="R72" s="134" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S72" s="134"/>
       <c r="T72" s="134"/>
@@ -21762,7 +21752,7 @@
       <c r="M77" s="35"/>
       <c r="N77" s="35"/>
       <c r="P77" s="142">
-        <f>'Данные объект'!B6</f>
+        <f>IF('Данные объект'!B6="","",'Данные объект'!B6)</f>
       </c>
       <c r="Q77" s="142"/>
       <c r="R77" s="142"/>
@@ -21787,7 +21777,7 @@
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
       <c r="P78" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="Q78" s="142"/>
       <c r="R78" s="142"/>
@@ -21816,7 +21806,7 @@
     </row>
     <row r="81" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B81" s="149"/>
       <c r="C81" s="149"/>
@@ -21934,7 +21924,7 @@
     </row>
     <row r="84" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="139" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B84" s="140"/>
       <c r="C84" s="140"/>
@@ -21979,7 +21969,7 @@
     </row>
     <row r="86" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="134" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B86" s="134"/>
       <c r="C86" s="134"/>
@@ -22098,7 +22088,7 @@
     </row>
     <row r="90" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H90" s="134"/>
       <c r="I90" s="134"/>
@@ -22114,10 +22104,10 @@
     </row>
     <row r="93" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B93" s="149">
-        <f>G72</f>
+        <f>IF(G72="","",G72)</f>
       </c>
       <c r="C93" s="149"/>
       <c r="D93" s="149"/>
@@ -22134,10 +22124,10 @@
       <c r="O93" s="149"/>
       <c r="P93" s="149"/>
       <c r="Q93" s="31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R93" s="31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S93" s="31"/>
       <c r="T93" s="31"/>
@@ -22160,10 +22150,10 @@
     </row>
     <row r="94" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B94" s="162" t="str">
-        <f>R72</f>
+        <f>IF(R72="","",R72)</f>
       </c>
       <c r="C94" s="162"/>
       <c r="D94" s="162"/>
@@ -22180,10 +22170,10 @@
       <c r="O94" s="162"/>
       <c r="P94" s="162"/>
       <c r="Q94" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R94" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S94" s="34"/>
       <c r="T94" s="34"/>
@@ -22294,7 +22284,7 @@
     </row>
     <row r="99" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="134" t="str">
-        <f>'Данные объект'!B33</f>
+        <f>IF('Данные объект'!B33="","",'Данные объект'!B33)</f>
       </c>
       <c r="B99" s="134"/>
       <c r="C99" s="134"/>
@@ -22381,7 +22371,7 @@
     </row>
     <row r="102" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="134" t="str">
-        <f>'Данные объект'!B20</f>
+        <f>IF('Данные объект'!B20="","",'Данные объект'!B20)</f>
       </c>
       <c r="B102" s="134"/>
       <c r="C102" s="134"/>
@@ -22473,7 +22463,7 @@
     </row>
     <row r="106" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="134" t="str">
-        <f>'Данные объект'!B17</f>
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
       </c>
       <c r="B106" s="134"/>
       <c r="C106" s="134"/>
@@ -22595,7 +22585,7 @@
     </row>
     <row r="109" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A109" s="134" t="str">
-        <f>'Данные объект'!$B$36</f>
+        <f>IF('Данные объект'!$B$36="","",'Данные объект'!$B$36)</f>
       </c>
       <c r="B109" s="134"/>
       <c r="C109" s="134"/>
@@ -22677,7 +22667,7 @@
     </row>
     <row r="111" spans="1:36" s="20" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B111" s="143"/>
       <c r="C111" s="143"/>
@@ -22717,7 +22707,7 @@
     </row>
     <row r="112" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B112" s="134"/>
       <c r="C112" s="134"/>
@@ -22746,7 +22736,7 @@
       <c r="Z112" s="35"/>
       <c r="AA112" s="35"/>
       <c r="AB112" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC112" s="134"/>
       <c r="AD112" s="134"/>
@@ -22801,7 +22791,7 @@
     </row>
     <row r="114" spans="1:36" s="20" customFormat="1" ht="40.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B114" s="143"/>
       <c r="C114" s="143"/>
@@ -22840,9 +22830,7 @@
       <c r="AJ114" s="143"/>
     </row>
     <row r="115" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="134" t="e">
-        <f>#REF!</f>
-      </c>
+      <c r="A115" s="134"/>
       <c r="B115" s="134"/>
       <c r="C115" s="134"/>
       <c r="D115" s="134"/>
@@ -23058,7 +23046,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AJ1" s="21"/>
+      <c r="AJ1" s="21" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" spans="1:43" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AJ2" s="21" t="s">
@@ -23080,7 +23070,7 @@
     </row>
     <row r="4" spans="1:43" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="138" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
@@ -23120,7 +23110,7 @@
     </row>
     <row r="5" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138" t="str">
-        <f>'Данные объект'!B9</f>
+        <f>IF('Данные объект'!B9="","",'Данные объект'!B9)</f>
       </c>
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
@@ -23200,7 +23190,7 @@
     </row>
     <row r="7" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="137"/>
       <c r="C7" s="137"/>
@@ -23240,7 +23230,7 @@
     </row>
     <row r="8" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="146" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="B8" s="146"/>
       <c r="C8" s="146"/>
@@ -23280,7 +23270,7 @@
     </row>
     <row r="9" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="140"/>
       <c r="C9" s="140"/>
@@ -23320,7 +23310,7 @@
     </row>
     <row r="10" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="146" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="B10" s="146"/>
       <c r="C10" s="146"/>
@@ -23360,7 +23350,7 @@
     </row>
     <row r="11" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="140"/>
       <c r="C11" s="140"/>
@@ -23400,7 +23390,7 @@
     </row>
     <row r="12" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="146" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="B12" s="146"/>
       <c r="C12" s="146"/>
@@ -23440,7 +23430,7 @@
     </row>
     <row r="13" spans="1:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="140"/>
       <c r="C13" s="140"/>
@@ -23485,7 +23475,7 @@
     </row>
     <row r="15" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="146" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B15" s="146"/>
       <c r="C15" s="146"/>
@@ -23565,7 +23555,7 @@
     </row>
     <row r="17" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B17" s="146"/>
       <c r="C17" s="146"/>
@@ -23605,7 +23595,7 @@
     </row>
     <row r="18" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="140"/>
       <c r="C18" s="140"/>
@@ -23645,7 +23635,7 @@
     </row>
     <row r="19" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B19" s="146"/>
       <c r="C19" s="146"/>
@@ -23685,7 +23675,7 @@
     </row>
     <row r="20" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="140"/>
       <c r="C20" s="140"/>
@@ -23730,7 +23720,7 @@
     </row>
     <row r="22" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="146" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="B22" s="146"/>
       <c r="C22" s="146"/>
@@ -23810,7 +23800,7 @@
     </row>
     <row r="24" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B24" s="146"/>
       <c r="C24" s="146"/>
@@ -23850,7 +23840,7 @@
     </row>
     <row r="25" spans="1:36" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="140"/>
       <c r="C25" s="140"/>
@@ -23890,7 +23880,7 @@
     </row>
     <row r="26" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B26" s="146"/>
       <c r="C26" s="146"/>
@@ -23930,7 +23920,7 @@
     </row>
     <row r="27" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" s="140"/>
       <c r="C27" s="140"/>
@@ -24083,11 +24073,11 @@
         <v>18</v>
       </c>
       <c r="C32" s="134">
-        <f>'АОСР-3'!C32:D32+1</f>
+        <f>IF('АОСР-3'!C32="","",'АОСР-3'!C32+1)</f>
       </c>
       <c r="D32" s="134"/>
       <c r="E32" s="134" t="str">
-        <f>'АОСР-1'!E33</f>
+        <f>IF('АОСР-1'!E33="","",'АОСР-1'!E33)</f>
       </c>
       <c r="F32" s="134"/>
       <c r="G32" s="134"/>
@@ -24098,7 +24088,7 @@
       <c r="Y32" s="35"/>
       <c r="Z32" s="35"/>
       <c r="AB32" s="142">
-        <f>P80</f>
+        <f>IF(P80="","",P80)</f>
       </c>
       <c r="AC32" s="142"/>
       <c r="AD32" s="142"/>
@@ -24135,7 +24125,7 @@
     </row>
     <row r="35" spans="1:36" s="20" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="137"/>
       <c r="C35" s="137"/>
@@ -24175,7 +24165,7 @@
     </row>
     <row r="36" spans="1:36" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="138" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="B36" s="138"/>
       <c r="C36" s="138"/>
@@ -24215,7 +24205,7 @@
     </row>
     <row r="37" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B37" s="140"/>
       <c r="C37" s="140"/>
@@ -24255,7 +24245,7 @@
     </row>
     <row r="38" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="138" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -24295,7 +24285,7 @@
     </row>
     <row r="39" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="151"/>
@@ -24340,7 +24330,7 @@
     </row>
     <row r="41" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="146" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
       <c r="B41" s="146"/>
       <c r="C41" s="146"/>
@@ -24420,7 +24410,7 @@
     </row>
     <row r="43" spans="1:36" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -24460,7 +24450,7 @@
     </row>
     <row r="44" spans="1:36" s="28" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="138" t="str">
-        <f>'Данные объект'!C18</f>
+        <f>IF('Данные объект'!C18="","",'Данные объект'!C18)</f>
       </c>
       <c r="B44" s="138"/>
       <c r="C44" s="138"/>
@@ -24500,7 +24490,7 @@
     </row>
     <row r="45" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="140"/>
       <c r="C45" s="140"/>
@@ -24580,7 +24570,7 @@
     </row>
     <row r="47" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="138" t="str">
-        <f>'Данные объект'!$C$36</f>
+        <f>IF('Данные объект'!$C$36="","",'Данные объект'!$C$36)</f>
       </c>
       <c r="B47" s="138"/>
       <c r="C47" s="138"/>
@@ -24660,7 +24650,7 @@
     </row>
     <row r="49" spans="1:36" s="20" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" s="143"/>
       <c r="C49" s="143"/>
@@ -24738,7 +24728,7 @@
     </row>
     <row r="51" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" s="140"/>
       <c r="C51" s="140"/>
@@ -24778,7 +24768,7 @@
     </row>
     <row r="52" spans="1:36" s="20" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="143"/>
@@ -24934,7 +24924,7 @@
     </row>
     <row r="56" spans="1:36" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="139"/>
       <c r="C56" s="139"/>
@@ -24979,7 +24969,7 @@
     </row>
     <row r="58" spans="1:36" s="20" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="134" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B58" s="134"/>
       <c r="C58" s="134"/>
@@ -25079,7 +25069,7 @@
       <c r="G62" s="163"/>
       <c r="H62" s="163"/>
       <c r="I62" s="156" t="str">
-        <f>'АОСР-1'!O63</f>
+        <f>IF('АОСР-1'!O63="","",'АОСР-1'!O63)</f>
       </c>
       <c r="J62" s="156"/>
       <c r="K62" s="156"/>
@@ -25090,7 +25080,7 @@
       <c r="N62" s="88"/>
       <c r="O62" s="88"/>
       <c r="P62" s="156">
-        <f>'АОСР-3'!T62</f>
+        <f>IF('АОСР-3'!T62="","",'АОСР-3'!T62)</f>
       </c>
       <c r="Q62" s="156"/>
       <c r="R62" s="156"/>
@@ -25197,7 +25187,7 @@
     </row>
     <row r="65" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="156" t="str">
-        <f>'Данные объект'!B43</f>
+        <f>IF('Данные объект'!B43="","",'Данные объект'!B43)</f>
       </c>
       <c r="B65" s="156"/>
       <c r="C65" s="156"/>
@@ -25332,7 +25322,7 @@
       <c r="N68" s="90"/>
       <c r="O68" s="90"/>
       <c r="P68" s="160" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q68" s="160"/>
       <c r="R68" s="160"/>
@@ -25357,7 +25347,7 @@
     </row>
     <row r="69" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="161" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B69" s="161"/>
       <c r="C69" s="161"/>
@@ -25365,11 +25355,9 @@
       <c r="E69" s="161"/>
       <c r="F69" s="161"/>
       <c r="G69" s="104" t="s">
-        <v>72</v>
-      </c>
-      <c r="H69" s="157">
-        <v>12</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H69" s="157"/>
       <c r="I69" s="157"/>
       <c r="J69" s="106" t="s">
         <v>141</v>
@@ -25413,11 +25401,9 @@
       <c r="E70" s="161"/>
       <c r="F70" s="161"/>
       <c r="G70" s="104" t="s">
-        <v>72</v>
-      </c>
-      <c r="H70" s="157">
-        <v>32</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H70" s="157"/>
       <c r="I70" s="157"/>
       <c r="J70" s="108" t="s">
         <v>141</v>
@@ -25461,11 +25447,9 @@
       <c r="E71" s="161"/>
       <c r="F71" s="161"/>
       <c r="G71" s="104" t="s">
-        <v>72</v>
-      </c>
-      <c r="H71" s="157">
-        <v>6</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H71" s="157"/>
       <c r="I71" s="157"/>
       <c r="J71" s="109" t="s">
         <v>141</v>
@@ -25501,7 +25485,7 @@
     </row>
     <row r="72" spans="1:36" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="158" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B72" s="159"/>
       <c r="C72" s="159"/>
@@ -25565,7 +25549,7 @@
       <c r="P74" s="31"/>
       <c r="Q74" s="31"/>
       <c r="R74" s="134" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S74" s="134"/>
       <c r="T74" s="134"/>
@@ -25754,7 +25738,7 @@
       <c r="M79" s="35"/>
       <c r="N79" s="35"/>
       <c r="P79" s="142">
-        <f>'Данные объект'!B6</f>
+        <f>IF('Данные объект'!B6="","",'Данные объект'!B6)</f>
       </c>
       <c r="Q79" s="142"/>
       <c r="R79" s="142"/>
@@ -25779,7 +25763,7 @@
       <c r="M80" s="35"/>
       <c r="N80" s="35"/>
       <c r="P80" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="Q80" s="142"/>
       <c r="R80" s="142"/>
@@ -25808,7 +25792,7 @@
     </row>
     <row r="83" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B83" s="149"/>
       <c r="C83" s="149"/>
@@ -25893,7 +25877,7 @@
     </row>
     <row r="86" spans="1:36" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="134" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" s="134"/>
       <c r="C86" s="134"/>
@@ -26051,7 +26035,7 @@
     </row>
     <row r="90" spans="1:36" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
@@ -26136,10 +26120,10 @@
     </row>
     <row r="93" spans="1:36" s="20" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B93" s="149">
-        <f>G74</f>
+        <f>IF(G74="","",G74)</f>
       </c>
       <c r="C93" s="149"/>
       <c r="D93" s="149"/>
@@ -26156,10 +26140,10 @@
       <c r="O93" s="149"/>
       <c r="P93" s="149"/>
       <c r="Q93" s="31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R93" s="31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S93" s="31"/>
       <c r="T93" s="31"/>
@@ -26220,10 +26204,10 @@
     </row>
     <row r="95" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B95" s="121" t="str">
-        <f>R74</f>
+        <f>IF(R74="","",R74)</f>
       </c>
       <c r="C95" s="121"/>
       <c r="D95" s="121"/>
@@ -26240,10 +26224,10 @@
       <c r="O95" s="121"/>
       <c r="P95" s="121"/>
       <c r="Q95" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R95" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S95" s="34"/>
       <c r="T95" s="34"/>
@@ -26266,10 +26250,10 @@
     </row>
     <row r="96" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B96" s="37" t="str">
-        <f>L69</f>
+        <f>IF(L69="","",L69)</f>
       </c>
       <c r="C96" s="37"/>
       <c r="D96" s="37"/>
@@ -26286,10 +26270,10 @@
       <c r="O96" s="37"/>
       <c r="P96" s="37"/>
       <c r="Q96" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R96" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S96" s="34"/>
       <c r="T96" s="34"/>
@@ -26312,10 +26296,10 @@
     </row>
     <row r="97" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B97" s="121" t="str">
-        <f>L70</f>
+        <f>IF(L70="","",L70)</f>
       </c>
       <c r="C97" s="121"/>
       <c r="D97" s="121"/>
@@ -26332,10 +26316,10 @@
       <c r="O97" s="121"/>
       <c r="P97" s="121"/>
       <c r="Q97" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R97" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S97" s="34"/>
       <c r="T97" s="34"/>
@@ -26361,7 +26345,7 @@
         <v>178</v>
       </c>
       <c r="B98" s="121" t="str">
-        <f>L71</f>
+        <f>IF(L71="","",L71)</f>
       </c>
       <c r="C98" s="121"/>
       <c r="D98" s="121"/>
@@ -26378,10 +26362,10 @@
       <c r="O98" s="121"/>
       <c r="P98" s="121"/>
       <c r="Q98" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R98" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S98" s="34"/>
       <c r="T98" s="34"/>
@@ -26454,7 +26438,7 @@
     </row>
     <row r="102" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="134" t="str">
-        <f>'Данные объект'!B33</f>
+        <f>IF('Данные объект'!B33="","",'Данные объект'!B33)</f>
       </c>
       <c r="B102" s="134"/>
       <c r="C102" s="134"/>
@@ -26541,7 +26525,7 @@
     </row>
     <row r="105" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="134" t="str">
-        <f>'Данные объект'!B20</f>
+        <f>IF('Данные объект'!B20="","",'Данные объект'!B20)</f>
       </c>
       <c r="B105" s="134"/>
       <c r="C105" s="134"/>
@@ -26633,7 +26617,7 @@
     </row>
     <row r="109" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="134" t="str">
-        <f>'Данные объект'!B17</f>
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
       </c>
       <c r="B109" s="134"/>
       <c r="C109" s="134"/>
@@ -26755,7 +26739,7 @@
     </row>
     <row r="112" spans="1:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="134" t="str">
-        <f>'Данные объект'!$B$36</f>
+        <f>IF('Данные объект'!$B$36="","",'Данные объект'!$B$36)</f>
       </c>
       <c r="B112" s="134"/>
       <c r="C112" s="134"/>
@@ -26837,7 +26821,7 @@
     </row>
     <row r="114" spans="1:36" s="20" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B114" s="143"/>
       <c r="C114" s="143"/>
@@ -26877,7 +26861,7 @@
     </row>
     <row r="115" spans="1:36" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B115" s="134"/>
       <c r="C115" s="134"/>
@@ -26906,7 +26890,7 @@
       <c r="Z115" s="35"/>
       <c r="AA115" s="35"/>
       <c r="AB115" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC115" s="134"/>
       <c r="AD115" s="134"/>
@@ -27088,7 +27072,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AJ1" s="21"/>
+      <c r="AJ1" s="21" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" spans="1:43" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AJ2" s="21" t="s">
@@ -27110,7 +27096,7 @@
     </row>
     <row r="4" spans="1:43" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="138" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
@@ -27150,7 +27136,7 @@
     </row>
     <row r="5" spans="1:43" s="20" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138" t="str">
-        <f>'Данные объект'!B9</f>
+        <f>IF('Данные объект'!B9="","",'Данные объект'!B9)</f>
       </c>
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
@@ -27230,7 +27216,7 @@
     </row>
     <row r="7" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="137"/>
       <c r="C7" s="137"/>
@@ -27270,7 +27256,7 @@
     </row>
     <row r="8" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="146" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="B8" s="146"/>
       <c r="C8" s="146"/>
@@ -27310,7 +27296,7 @@
     </row>
     <row r="9" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="140"/>
       <c r="C9" s="140"/>
@@ -27350,7 +27336,7 @@
     </row>
     <row r="10" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="146" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="B10" s="146"/>
       <c r="C10" s="146"/>
@@ -27390,7 +27376,7 @@
     </row>
     <row r="11" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="140"/>
       <c r="C11" s="140"/>
@@ -27430,7 +27416,7 @@
     </row>
     <row r="12" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="146" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="B12" s="146"/>
       <c r="C12" s="146"/>
@@ -27470,7 +27456,7 @@
     </row>
     <row r="13" spans="1:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="140"/>
       <c r="C13" s="140"/>
@@ -27515,7 +27501,7 @@
     </row>
     <row r="15" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="146" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B15" s="146"/>
       <c r="C15" s="146"/>
@@ -27595,7 +27581,7 @@
     </row>
     <row r="17" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B17" s="146"/>
       <c r="C17" s="146"/>
@@ -27635,7 +27621,7 @@
     </row>
     <row r="18" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="140"/>
       <c r="C18" s="140"/>
@@ -27675,7 +27661,7 @@
     </row>
     <row r="19" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B19" s="146"/>
       <c r="C19" s="146"/>
@@ -27715,7 +27701,7 @@
     </row>
     <row r="20" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="140"/>
       <c r="C20" s="140"/>
@@ -27760,7 +27746,7 @@
     </row>
     <row r="22" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="146" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="B22" s="146"/>
       <c r="C22" s="146"/>
@@ -27840,7 +27826,7 @@
     </row>
     <row r="24" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B24" s="146"/>
       <c r="C24" s="146"/>
@@ -27880,7 +27866,7 @@
     </row>
     <row r="25" spans="1:36" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="140"/>
       <c r="C25" s="140"/>
@@ -27920,7 +27906,7 @@
     </row>
     <row r="26" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B26" s="146"/>
       <c r="C26" s="146"/>
@@ -27960,7 +27946,7 @@
     </row>
     <row r="27" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" s="140"/>
       <c r="C27" s="140"/>
@@ -28113,11 +28099,11 @@
         <v>18</v>
       </c>
       <c r="C32" s="134">
-        <f>'АОСР-4'!C32:D32+1</f>
+        <f>IF('АОСР-4'!C32="","",'АОСР-4'!C32+1)</f>
       </c>
       <c r="D32" s="134"/>
       <c r="E32" s="134" t="str">
-        <f>'АОСР-1'!E33</f>
+        <f>IF('АОСР-1'!E33="","",'АОСР-1'!E33)</f>
       </c>
       <c r="F32" s="134"/>
       <c r="G32" s="134"/>
@@ -28128,7 +28114,7 @@
       <c r="Y32" s="35"/>
       <c r="Z32" s="35"/>
       <c r="AB32" s="142">
-        <f>P78</f>
+        <f>IF(P78="","",P78)</f>
       </c>
       <c r="AC32" s="142"/>
       <c r="AD32" s="142"/>
@@ -28165,7 +28151,7 @@
     </row>
     <row r="35" spans="1:36" s="20" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="137"/>
       <c r="C35" s="137"/>
@@ -28205,7 +28191,7 @@
     </row>
     <row r="36" spans="1:36" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="138" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="B36" s="138"/>
       <c r="C36" s="138"/>
@@ -28245,7 +28231,7 @@
     </row>
     <row r="37" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B37" s="140"/>
       <c r="C37" s="140"/>
@@ -28285,7 +28271,7 @@
     </row>
     <row r="38" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="138" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -28325,7 +28311,7 @@
     </row>
     <row r="39" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="151"/>
@@ -28370,7 +28356,7 @@
     </row>
     <row r="41" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="146" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
       <c r="B41" s="146"/>
       <c r="C41" s="146"/>
@@ -28450,7 +28436,7 @@
     </row>
     <row r="43" spans="1:36" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -28490,7 +28476,7 @@
     </row>
     <row r="44" spans="1:36" s="28" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="138" t="str">
-        <f>'Данные объект'!C18</f>
+        <f>IF('Данные объект'!C18="","",'Данные объект'!C18)</f>
       </c>
       <c r="B44" s="138"/>
       <c r="C44" s="138"/>
@@ -28530,7 +28516,7 @@
     </row>
     <row r="45" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="140"/>
       <c r="C45" s="140"/>
@@ -28610,7 +28596,7 @@
     </row>
     <row r="47" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="138" t="str">
-        <f>'Данные объект'!$C$36</f>
+        <f>IF('Данные объект'!$C$36="","",'Данные объект'!$C$36)</f>
       </c>
       <c r="B47" s="138"/>
       <c r="C47" s="138"/>
@@ -28690,7 +28676,7 @@
     </row>
     <row r="49" spans="1:36" s="20" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" s="143"/>
       <c r="C49" s="143"/>
@@ -28768,7 +28754,7 @@
     </row>
     <row r="51" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" s="140"/>
       <c r="C51" s="140"/>
@@ -28808,7 +28794,7 @@
     </row>
     <row r="52" spans="1:36" s="20" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="143"/>
@@ -28964,7 +28950,7 @@
     </row>
     <row r="56" spans="1:36" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="139"/>
       <c r="C56" s="139"/>
@@ -29009,7 +28995,7 @@
     </row>
     <row r="58" spans="1:36" s="20" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="134" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B58" s="134"/>
       <c r="C58" s="134"/>
@@ -29114,7 +29100,7 @@
       <c r="L62" s="146"/>
       <c r="M62" s="146"/>
       <c r="N62" s="138" t="str">
-        <f>'АОСР-1'!O63</f>
+        <f>IF('АОСР-1'!O63="","",'АОСР-1'!O63)</f>
       </c>
       <c r="O62" s="138"/>
       <c r="P62" s="138"/>
@@ -29125,7 +29111,7 @@
       <c r="S62" s="29"/>
       <c r="T62" s="29"/>
       <c r="U62" s="156">
-        <f>'АОСР-3'!T62</f>
+        <f>IF('АОСР-3'!T62="","",'АОСР-3'!T62)</f>
       </c>
       <c r="V62" s="156"/>
       <c r="W62" s="156"/>
@@ -29134,7 +29120,7 @@
       </c>
       <c r="Y62" s="29"/>
       <c r="Z62" s="156">
-        <f>'АОСР-3'!X62</f>
+        <f>IF('АОСР-3'!X62="","",'АОСР-3'!X62)</f>
       </c>
       <c r="AA62" s="156"/>
       <c r="AB62" s="29"/>
@@ -29196,7 +29182,7 @@
     </row>
     <row r="65" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="138" t="str">
-        <f>'Данные объект'!B43</f>
+        <f>IF('Данные объект'!B43="","",'Данные объект'!B43)</f>
       </c>
       <c r="B65" s="138"/>
       <c r="C65" s="138"/>
@@ -29319,7 +29305,7 @@
       <c r="N68" s="9"/>
       <c r="O68" s="9"/>
       <c r="P68" s="136" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q68" s="136"/>
       <c r="R68" s="136"/>
@@ -29441,7 +29427,7 @@
       <c r="P72" s="31"/>
       <c r="Q72" s="31"/>
       <c r="R72" s="134" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S72" s="134"/>
       <c r="T72" s="134"/>
@@ -29630,7 +29616,7 @@
       <c r="M77" s="35"/>
       <c r="N77" s="35"/>
       <c r="P77" s="142">
-        <f>'Данные объект'!B6</f>
+        <f>IF('Данные объект'!B6="","",'Данные объект'!B6)</f>
       </c>
       <c r="Q77" s="142"/>
       <c r="R77" s="142"/>
@@ -29655,7 +29641,7 @@
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
       <c r="P78" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="Q78" s="142"/>
       <c r="R78" s="142"/>
@@ -29684,7 +29670,7 @@
     </row>
     <row r="81" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B81" s="149"/>
       <c r="C81" s="149"/>
@@ -29802,7 +29788,7 @@
     </row>
     <row r="84" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="135" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B84" s="135"/>
       <c r="C84" s="135"/>
@@ -29966,7 +29952,7 @@
     </row>
     <row r="90" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H90" s="134"/>
       <c r="I90" s="134"/>
@@ -29982,10 +29968,10 @@
     </row>
     <row r="93" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B93" s="162" t="str">
-        <f>R72</f>
+        <f>IF(R72="","",R72)</f>
       </c>
       <c r="C93" s="162"/>
       <c r="D93" s="162"/>
@@ -30002,10 +29988,10 @@
       <c r="O93" s="162"/>
       <c r="P93" s="162"/>
       <c r="Q93" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R93" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S93" s="18"/>
       <c r="T93" s="18"/>
@@ -30116,7 +30102,7 @@
     </row>
     <row r="98" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="134" t="str">
-        <f>'Данные объект'!B33</f>
+        <f>IF('Данные объект'!B33="","",'Данные объект'!B33)</f>
       </c>
       <c r="B98" s="134"/>
       <c r="C98" s="134"/>
@@ -30203,7 +30189,7 @@
     </row>
     <row r="101" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="134" t="str">
-        <f>'Данные объект'!B20</f>
+        <f>IF('Данные объект'!B20="","",'Данные объект'!B20)</f>
       </c>
       <c r="B101" s="134"/>
       <c r="C101" s="134"/>
@@ -30295,7 +30281,7 @@
     </row>
     <row r="105" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="134" t="str">
-        <f>'Данные объект'!B17</f>
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
       </c>
       <c r="B105" s="134"/>
       <c r="C105" s="134"/>
@@ -30417,7 +30403,7 @@
     </row>
     <row r="108" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A108" s="134" t="str">
-        <f>'Данные объект'!$B$36</f>
+        <f>IF('Данные объект'!$B$36="","",'Данные объект'!$B$36)</f>
       </c>
       <c r="B108" s="134"/>
       <c r="C108" s="134"/>
@@ -30499,7 +30485,7 @@
     </row>
     <row r="110" spans="1:36" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B110" s="143"/>
       <c r="C110" s="143"/>
@@ -30539,7 +30525,7 @@
     </row>
     <row r="111" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B111" s="134"/>
       <c r="C111" s="134"/>
@@ -30568,7 +30554,7 @@
       <c r="Z111" s="35"/>
       <c r="AA111" s="35"/>
       <c r="AB111" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC111" s="134"/>
       <c r="AD111" s="134"/>
@@ -30623,7 +30609,7 @@
     </row>
     <row r="113" spans="1:36" s="20" customFormat="1" ht="11.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B113" s="143"/>
       <c r="C113" s="143"/>
@@ -30662,9 +30648,7 @@
       <c r="AJ113" s="143"/>
     </row>
     <row r="114" spans="1:36" s="20" customFormat="1" ht="11.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="134" t="e">
-        <f>#REF!</f>
-      </c>
+      <c r="A114" s="134"/>
       <c r="B114" s="134"/>
       <c r="C114" s="134"/>
       <c r="D114" s="134"/>
@@ -30878,7 +30862,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AJ1" s="21"/>
+      <c r="AJ1" s="21" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" spans="1:43" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AJ2" s="21" t="s">
@@ -30900,7 +30886,7 @@
     </row>
     <row r="4" spans="1:43" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="138" t="str">
-        <f>'Данные объект'!B3</f>
+        <f>IF('Данные объект'!B3="","",'Данные объект'!B3)</f>
       </c>
       <c r="B4" s="138"/>
       <c r="C4" s="138"/>
@@ -30940,7 +30926,7 @@
     </row>
     <row r="5" spans="1:43" s="20" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138" t="str">
-        <f>'Данные объект'!B9</f>
+        <f>IF('Данные объект'!B9="","",'Данные объект'!B9)</f>
       </c>
       <c r="B5" s="138"/>
       <c r="C5" s="138"/>
@@ -31020,7 +31006,7 @@
     </row>
     <row r="7" spans="1:43" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="137"/>
       <c r="C7" s="137"/>
@@ -31060,7 +31046,7 @@
     </row>
     <row r="8" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="146" t="str">
-        <f>'Данные объект'!B23</f>
+        <f>IF('Данные объект'!B23="","",'Данные объект'!B23)</f>
       </c>
       <c r="B8" s="146"/>
       <c r="C8" s="146"/>
@@ -31100,7 +31086,7 @@
     </row>
     <row r="9" spans="1:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="139" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="140"/>
       <c r="C9" s="140"/>
@@ -31140,7 +31126,7 @@
     </row>
     <row r="10" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="146" t="str">
-        <f>'Данные объект'!B24</f>
+        <f>IF('Данные объект'!B24="","",'Данные объект'!B24)</f>
       </c>
       <c r="B10" s="146"/>
       <c r="C10" s="146"/>
@@ -31180,7 +31166,7 @@
     </row>
     <row r="11" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="139" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="140"/>
       <c r="C11" s="140"/>
@@ -31220,7 +31206,7 @@
     </row>
     <row r="12" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="146" t="str">
-        <f>'Данные объект'!B25</f>
+        <f>IF('Данные объект'!B25="","",'Данные объект'!B25)</f>
       </c>
       <c r="B12" s="146"/>
       <c r="C12" s="146"/>
@@ -31260,7 +31246,7 @@
     </row>
     <row r="13" spans="1:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="140"/>
       <c r="C13" s="140"/>
@@ -31305,7 +31291,7 @@
     </row>
     <row r="15" spans="1:43" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="146" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B15" s="146"/>
       <c r="C15" s="146"/>
@@ -31385,7 +31371,7 @@
     </row>
     <row r="17" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B17" s="146"/>
       <c r="C17" s="146"/>
@@ -31425,7 +31411,7 @@
     </row>
     <row r="18" spans="1:36" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="140"/>
       <c r="C18" s="140"/>
@@ -31465,7 +31451,7 @@
     </row>
     <row r="19" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B19" s="146"/>
       <c r="C19" s="146"/>
@@ -31505,7 +31491,7 @@
     </row>
     <row r="20" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="139" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="140"/>
       <c r="C20" s="140"/>
@@ -31550,7 +31536,7 @@
     </row>
     <row r="22" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="146" t="str">
-        <f>'Данные объект'!B39</f>
+        <f>IF('Данные объект'!B39="","",'Данные объект'!B39)</f>
       </c>
       <c r="B22" s="146"/>
       <c r="C22" s="146"/>
@@ -31630,7 +31616,7 @@
     </row>
     <row r="24" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="146" t="str">
-        <f>'Данные объект'!B12</f>
+        <f>IF('Данные объект'!B12="","",'Данные объект'!B12)</f>
       </c>
       <c r="B24" s="146"/>
       <c r="C24" s="146"/>
@@ -31670,7 +31656,7 @@
     </row>
     <row r="25" spans="1:36" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="139" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="140"/>
       <c r="C25" s="140"/>
@@ -31710,7 +31696,7 @@
     </row>
     <row r="26" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="146" t="str">
-        <f>'Данные объект'!B13</f>
+        <f>IF('Данные объект'!B13="","",'Данные объект'!B13)</f>
       </c>
       <c r="B26" s="146"/>
       <c r="C26" s="146"/>
@@ -31750,7 +31736,7 @@
     </row>
     <row r="27" spans="1:36" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" s="140"/>
       <c r="C27" s="140"/>
@@ -31903,11 +31889,11 @@
         <v>18</v>
       </c>
       <c r="C32" s="134">
-        <f>'АОСР-5'!C32:D32+1</f>
+        <f>IF('АОСР-5'!C32="","",'АОСР-5'!C32+1)</f>
       </c>
       <c r="D32" s="134"/>
       <c r="E32" s="134" t="str">
-        <f>'АОСР-1'!E33</f>
+        <f>IF('АОСР-1'!E33="","",'АОСР-1'!E33)</f>
       </c>
       <c r="F32" s="134"/>
       <c r="G32" s="134"/>
@@ -31918,7 +31904,7 @@
       <c r="Y32" s="35"/>
       <c r="Z32" s="35"/>
       <c r="AB32" s="142">
-        <f>P78</f>
+        <f>IF(P78="","",P78)</f>
       </c>
       <c r="AC32" s="142"/>
       <c r="AD32" s="142"/>
@@ -31955,7 +31941,7 @@
     </row>
     <row r="35" spans="1:36" s="20" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="137"/>
       <c r="C35" s="137"/>
@@ -31995,7 +31981,7 @@
     </row>
     <row r="36" spans="1:36" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="138" t="str">
-        <f>'Данные объект'!C34</f>
+        <f>IF('Данные объект'!C34="","",'Данные объект'!C34)</f>
       </c>
       <c r="B36" s="138"/>
       <c r="C36" s="138"/>
@@ -32035,7 +32021,7 @@
     </row>
     <row r="37" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="139" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B37" s="140"/>
       <c r="C37" s="140"/>
@@ -32075,7 +32061,7 @@
     </row>
     <row r="38" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="138" t="str">
-        <f>'Данные объект'!C23</f>
+        <f>IF('Данные объект'!C23="","",'Данные объект'!C23)</f>
       </c>
       <c r="B38" s="138"/>
       <c r="C38" s="138"/>
@@ -32115,7 +32101,7 @@
     </row>
     <row r="39" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="151"/>
@@ -32160,7 +32146,7 @@
     </row>
     <row r="41" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="146" t="str">
-        <f>'Данные объект'!C21</f>
+        <f>IF('Данные объект'!C21="","",'Данные объект'!C21)</f>
       </c>
       <c r="B41" s="146"/>
       <c r="C41" s="146"/>
@@ -32240,7 +32226,7 @@
     </row>
     <row r="43" spans="1:36" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -32280,7 +32266,7 @@
     </row>
     <row r="44" spans="1:36" s="28" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="138" t="str">
-        <f>'Данные объект'!C18</f>
+        <f>IF('Данные объект'!C18="","",'Данные объект'!C18)</f>
       </c>
       <c r="B44" s="138"/>
       <c r="C44" s="138"/>
@@ -32320,7 +32306,7 @@
     </row>
     <row r="45" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="140"/>
       <c r="C45" s="140"/>
@@ -32400,7 +32386,7 @@
     </row>
     <row r="47" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="138" t="str">
-        <f>'Данные объект'!$C$36</f>
+        <f>IF('Данные объект'!$C$36="","",'Данные объект'!$C$36)</f>
       </c>
       <c r="B47" s="138"/>
       <c r="C47" s="138"/>
@@ -32480,7 +32466,7 @@
     </row>
     <row r="49" spans="1:36" s="20" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" s="143"/>
       <c r="C49" s="143"/>
@@ -32558,7 +32544,7 @@
     </row>
     <row r="51" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" s="140"/>
       <c r="C51" s="140"/>
@@ -32598,7 +32584,7 @@
     </row>
     <row r="52" spans="1:36" s="20" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="143"/>
@@ -32754,7 +32740,7 @@
     </row>
     <row r="56" spans="1:36" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="139"/>
       <c r="C56" s="139"/>
@@ -32799,7 +32785,7 @@
     </row>
     <row r="58" spans="1:36" s="20" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="134" t="str">
-        <f>'Данные объект'!B11</f>
+        <f>IF('Данные объект'!B11="","",'Данные объект'!B11)</f>
       </c>
       <c r="B58" s="134"/>
       <c r="C58" s="134"/>
@@ -32888,8 +32874,8 @@
       </c>
     </row>
     <row r="62" spans="1:36" s="20" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="146" t="str">
-        <f>'АОСР-5'!A86:AJ86</f>
+      <c r="A62" s="146">
+        <f>IF('АОСР-5'!A86="","",'АОСР-5'!A86)</f>
       </c>
       <c r="B62" s="146"/>
       <c r="C62" s="146"/>
@@ -32904,7 +32890,7 @@
       <c r="L62" s="146"/>
       <c r="M62" s="146"/>
       <c r="Q62" s="138" t="str">
-        <f>'АОСР-1'!O63</f>
+        <f>IF('АОСР-1'!O63="","",'АОСР-1'!O63)</f>
       </c>
       <c r="R62" s="138"/>
       <c r="S62" s="138"/>
@@ -32973,7 +32959,7 @@
     </row>
     <row r="65" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="138" t="str">
-        <f>'Данные объект'!B43</f>
+        <f>IF('Данные объект'!B43="","",'Данные объект'!B43)</f>
       </c>
       <c r="B65" s="138"/>
       <c r="C65" s="138"/>
@@ -33094,7 +33080,7 @@
       <c r="N68" s="9"/>
       <c r="O68" s="9"/>
       <c r="P68" s="136" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q68" s="136"/>
       <c r="R68" s="136"/>
@@ -33127,11 +33113,9 @@
       <c r="E69" s="161"/>
       <c r="F69" s="161"/>
       <c r="G69" s="104" t="s">
-        <v>72</v>
-      </c>
-      <c r="H69" s="157">
-        <v>12</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H69" s="157"/>
       <c r="I69" s="157"/>
       <c r="J69" s="106" t="s">
         <v>141</v>
@@ -33177,7 +33161,7 @@
       <c r="E70" s="161"/>
       <c r="F70" s="161"/>
       <c r="G70" s="104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H70" s="157"/>
       <c r="I70" s="157"/>
@@ -33423,7 +33407,7 @@
       <c r="M77" s="35"/>
       <c r="N77" s="35"/>
       <c r="P77" s="142">
-        <f>'Данные объект'!B6</f>
+        <f>IF('Данные объект'!B6="","",'Данные объект'!B6)</f>
       </c>
       <c r="Q77" s="142"/>
       <c r="R77" s="142"/>
@@ -33448,7 +33432,7 @@
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
       <c r="P78" s="142">
-        <f>'Данные объект'!B7</f>
+        <f>IF('Данные объект'!B7="","",'Данные объект'!B7)</f>
       </c>
       <c r="Q78" s="142"/>
       <c r="R78" s="142"/>
@@ -33477,7 +33461,7 @@
     </row>
     <row r="81" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B81" s="149"/>
       <c r="C81" s="149"/>
@@ -33595,7 +33579,7 @@
     </row>
     <row r="84" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="135" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B84" s="135"/>
       <c r="C84" s="135"/>
@@ -33759,7 +33743,7 @@
     </row>
     <row r="90" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H90" s="134"/>
       <c r="I90" s="134"/>
@@ -33775,10 +33759,10 @@
     </row>
     <row r="93" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B93" s="162" t="str">
-        <f>R72</f>
+        <f>IF(R72="","",R72)</f>
       </c>
       <c r="C93" s="162"/>
       <c r="D93" s="162"/>
@@ -33795,10 +33779,10 @@
       <c r="O93" s="162"/>
       <c r="P93" s="162"/>
       <c r="Q93" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R93" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S93" s="18"/>
       <c r="T93" s="18"/>
@@ -33821,10 +33805,10 @@
     </row>
     <row r="94" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B94" s="162" t="str">
-        <f>L69</f>
+        <f>IF(L69="","",L69)</f>
       </c>
       <c r="C94" s="162"/>
       <c r="D94" s="162"/>
@@ -33841,10 +33825,10 @@
       <c r="O94" s="162"/>
       <c r="P94" s="162"/>
       <c r="Q94" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R94" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S94" s="18"/>
       <c r="T94" s="18"/>
@@ -33867,10 +33851,10 @@
     </row>
     <row r="95" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B95" s="162" t="str">
-        <f>L70</f>
+        <f>IF(L70="","",L70)</f>
       </c>
       <c r="C95" s="162"/>
       <c r="D95" s="162"/>
@@ -33887,10 +33871,10 @@
       <c r="O95" s="162"/>
       <c r="P95" s="162"/>
       <c r="Q95" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R95" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S95" s="18"/>
       <c r="T95" s="18"/>
@@ -34001,7 +33985,7 @@
     </row>
     <row r="100" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="134" t="str">
-        <f>'Данные объект'!B33</f>
+        <f>IF('Данные объект'!B33="","",'Данные объект'!B33)</f>
       </c>
       <c r="B100" s="134"/>
       <c r="C100" s="134"/>
@@ -34088,7 +34072,7 @@
     </row>
     <row r="103" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="134" t="str">
-        <f>'Данные объект'!B20</f>
+        <f>IF('Данные объект'!B20="","",'Данные объект'!B20)</f>
       </c>
       <c r="B103" s="134"/>
       <c r="C103" s="134"/>
@@ -34180,7 +34164,7 @@
     </row>
     <row r="107" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="134" t="str">
-        <f>'Данные объект'!B17</f>
+        <f>IF('Данные объект'!B17="","",'Данные объект'!B17)</f>
       </c>
       <c r="B107" s="134"/>
       <c r="C107" s="134"/>
@@ -34302,7 +34286,7 @@
     </row>
     <row r="110" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A110" s="134" t="str">
-        <f>'Данные объект'!$B$36</f>
+        <f>IF('Данные объект'!$B$36="","",'Данные объект'!$B$36)</f>
       </c>
       <c r="B110" s="134"/>
       <c r="C110" s="134"/>
@@ -34384,7 +34368,7 @@
     </row>
     <row r="112" spans="1:36" s="20" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B112" s="143"/>
       <c r="C112" s="143"/>
@@ -34424,7 +34408,7 @@
     </row>
     <row r="113" spans="1:36" s="20" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B113" s="134"/>
       <c r="C113" s="134"/>
@@ -34453,7 +34437,7 @@
       <c r="Z113" s="35"/>
       <c r="AA113" s="35"/>
       <c r="AB113" s="134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC113" s="134"/>
       <c r="AD113" s="134"/>
@@ -34508,7 +34492,7 @@
     </row>
     <row r="115" spans="1:36" s="20" customFormat="1" ht="11.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="143" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B115" s="143"/>
       <c r="C115" s="143"/>
@@ -34547,9 +34531,7 @@
       <c r="AJ115" s="143"/>
     </row>
     <row r="116" spans="1:36" s="20" customFormat="1" ht="11.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="134" t="e">
-        <f>#REF!</f>
-      </c>
+      <c r="A116" s="134"/>
       <c r="B116" s="134"/>
       <c r="C116" s="134"/>
       <c r="D116" s="134"/>
